--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124164341</v>
+        <v>124163076</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455084</v>
+        <v>455065</v>
       </c>
       <c r="R2" t="n">
-        <v>6791213</v>
+        <v>6791354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124164315</v>
+        <v>124162358</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455046</v>
+        <v>455065</v>
       </c>
       <c r="R3" t="n">
-        <v>6791351</v>
+        <v>6791370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124163076</v>
+        <v>124164315</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455065</v>
+        <v>455046</v>
       </c>
       <c r="R4" t="n">
-        <v>6791354</v>
+        <v>6791351</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124162358</v>
+        <v>124164341</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455065</v>
+        <v>455084</v>
       </c>
       <c r="R5" t="n">
-        <v>6791370</v>
+        <v>6791213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466776</v>
+        <v>124466761</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1115,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454967</v>
+        <v>454973</v>
       </c>
       <c r="R6" t="n">
-        <v>6791549</v>
+        <v>6791596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1307,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466758</v>
+        <v>124466785</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,35 +1328,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454965</v>
+        <v>455002</v>
       </c>
       <c r="R8" t="n">
-        <v>6791575</v>
+        <v>6791543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466734</v>
+        <v>124466741</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,31 +1435,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455027</v>
+        <v>454985</v>
       </c>
       <c r="R9" t="n">
-        <v>6791520</v>
+        <v>6791568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466763</v>
+        <v>124466771</v>
       </c>
       <c r="B10" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455022</v>
+        <v>455011</v>
       </c>
       <c r="R10" t="n">
-        <v>6791480</v>
+        <v>6791455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466756</v>
+        <v>124466717</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,47 +1648,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454999</v>
+        <v>455070</v>
       </c>
       <c r="R11" t="n">
-        <v>6791433</v>
+        <v>6791371</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466760</v>
+        <v>124466774</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,47 +1750,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455024</v>
+        <v>455009</v>
       </c>
       <c r="R12" t="n">
-        <v>6791525</v>
+        <v>6791499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466716</v>
+        <v>124466728</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1852,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455041</v>
+        <v>454980</v>
       </c>
       <c r="R13" t="n">
-        <v>6791358</v>
+        <v>6791584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466785</v>
+        <v>124466776</v>
       </c>
       <c r="B14" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,43 +1954,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455002</v>
+        <v>454967</v>
       </c>
       <c r="R14" t="n">
-        <v>6791543</v>
+        <v>6791549</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466740</v>
+        <v>124466777</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,47 +2056,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455036</v>
+        <v>454993</v>
       </c>
       <c r="R15" t="n">
-        <v>6791428</v>
+        <v>6791588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,7 +2146,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466723</v>
+        <v>124466727</v>
       </c>
       <c r="B16" t="n">
         <v>91012</v>
@@ -2209,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455035</v>
+        <v>454951</v>
       </c>
       <c r="R16" t="n">
-        <v>6791359</v>
+        <v>6791583</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466777</v>
+        <v>124466716</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2260,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454993</v>
+        <v>455041</v>
       </c>
       <c r="R17" t="n">
-        <v>6791588</v>
+        <v>6791358</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466721</v>
+        <v>124466720</v>
       </c>
       <c r="B18" t="n">
-        <v>91361</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2362,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454980</v>
+        <v>455013</v>
       </c>
       <c r="R18" t="n">
-        <v>6791584</v>
+        <v>6791456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466757</v>
+        <v>124466724</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,47 +2575,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454954</v>
+        <v>455029</v>
       </c>
       <c r="R20" t="n">
-        <v>6791589</v>
+        <v>6791510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466745</v>
+        <v>124466763</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,47 +2779,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454974</v>
+        <v>455022</v>
       </c>
       <c r="R22" t="n">
-        <v>6791602</v>
+        <v>6791480</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2869,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466751</v>
+        <v>124466758</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2945,7 +2904,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2959,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454956</v>
+        <v>454965</v>
       </c>
       <c r="R23" t="n">
-        <v>6791586</v>
+        <v>6791575</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466771</v>
+        <v>124466743</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3033,38 +2992,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455011</v>
+        <v>454986</v>
       </c>
       <c r="R24" t="n">
-        <v>6791455</v>
+        <v>6791588</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466770</v>
+        <v>124466756</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,28 +3103,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
@@ -3225,10 +3202,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466730</v>
+        <v>124466760</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,31 +3214,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3270,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455093</v>
+        <v>455024</v>
       </c>
       <c r="R26" t="n">
-        <v>6791177</v>
+        <v>6791525</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,11 +3287,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466787</v>
+        <v>124466719</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,43 +3325,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455074</v>
+        <v>455046</v>
       </c>
       <c r="R27" t="n">
-        <v>6791202</v>
+        <v>6791403</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,11 +3389,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,10 +3415,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466727</v>
+        <v>124466730</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,34 +3431,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454951</v>
+        <v>455093</v>
       </c>
       <c r="R28" t="n">
-        <v>6791583</v>
+        <v>6791177</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,6 +3496,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466717</v>
+        <v>124466751</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,38 +3539,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455070</v>
+        <v>454956</v>
       </c>
       <c r="R29" t="n">
-        <v>6791371</v>
+        <v>6791586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466718</v>
+        <v>124466713</v>
       </c>
       <c r="B30" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3650,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455062</v>
+        <v>454998</v>
       </c>
       <c r="R30" t="n">
-        <v>6791378</v>
+        <v>6791464</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466728</v>
+        <v>124466753</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,38 +3752,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454980</v>
+        <v>454960</v>
       </c>
       <c r="R31" t="n">
-        <v>6791584</v>
+        <v>6791599</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3851,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466724</v>
+        <v>124466765</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3867,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455029</v>
+        <v>455018</v>
       </c>
       <c r="R32" t="n">
-        <v>6791510</v>
+        <v>6791399</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,10 +3953,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466775</v>
+        <v>124466723</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,21 +3969,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3999,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454990</v>
+        <v>455035</v>
       </c>
       <c r="R33" t="n">
-        <v>6791542</v>
+        <v>6791359</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466774</v>
+        <v>124466718</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,25 +4067,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4101,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455009</v>
+        <v>455062</v>
       </c>
       <c r="R34" t="n">
-        <v>6791499</v>
+        <v>6791378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,10 +4157,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466738</v>
+        <v>124466787</v>
       </c>
       <c r="B35" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,38 +4169,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454961</v>
+        <v>455074</v>
       </c>
       <c r="R35" t="n">
-        <v>6791550</v>
+        <v>6791202</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4239,6 +4238,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4265,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466765</v>
+        <v>124466721</v>
       </c>
       <c r="B36" t="n">
-        <v>91026</v>
+        <v>91361</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,25 +4281,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4305,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455018</v>
+        <v>454980</v>
       </c>
       <c r="R36" t="n">
-        <v>6791399</v>
+        <v>6791584</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4367,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466746</v>
+        <v>124466734</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4379,35 +4383,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454971</v>
+        <v>455027</v>
       </c>
       <c r="R37" t="n">
-        <v>6791601</v>
+        <v>6791520</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466753</v>
+        <v>124466775</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4490,47 +4490,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454960</v>
+        <v>454990</v>
       </c>
       <c r="R38" t="n">
-        <v>6791599</v>
+        <v>6791542</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466741</v>
+        <v>124466738</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,47 +4592,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454985</v>
+        <v>454961</v>
       </c>
       <c r="R39" t="n">
-        <v>6791568</v>
+        <v>6791550</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466713</v>
+        <v>124466740</v>
       </c>
       <c r="B40" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,38 +4694,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454998</v>
+        <v>455036</v>
       </c>
       <c r="R40" t="n">
-        <v>6791464</v>
+        <v>6791428</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466761</v>
+        <v>124466770</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,47 +4805,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454973</v>
+        <v>454999</v>
       </c>
       <c r="R41" t="n">
-        <v>6791596</v>
+        <v>6791433</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466743</v>
+        <v>124466745</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4948,7 +4930,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4962,10 +4944,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454986</v>
+        <v>454974</v>
       </c>
       <c r="R42" t="n">
-        <v>6791588</v>
+        <v>6791602</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5024,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466719</v>
+        <v>124466746</v>
       </c>
       <c r="B43" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,38 +5018,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455046</v>
+        <v>454971</v>
       </c>
       <c r="R43" t="n">
-        <v>6791403</v>
+        <v>6791601</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466720</v>
+        <v>124466757</v>
       </c>
       <c r="B44" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,38 +5129,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455013</v>
+        <v>454954</v>
       </c>
       <c r="R44" t="n">
-        <v>6791456</v>
+        <v>6791589</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124163076</v>
+        <v>124164315</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455065</v>
+        <v>455046</v>
       </c>
       <c r="R2" t="n">
-        <v>6791354</v>
+        <v>6791351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124164315</v>
+        <v>124164341</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455046</v>
+        <v>455084</v>
       </c>
       <c r="R4" t="n">
-        <v>6791351</v>
+        <v>6791213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124164341</v>
+        <v>124163076</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455084</v>
+        <v>455065</v>
       </c>
       <c r="R5" t="n">
-        <v>6791213</v>
+        <v>6791354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466761</v>
+        <v>124466716</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,47 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454973</v>
+        <v>455041</v>
       </c>
       <c r="R6" t="n">
-        <v>6791596</v>
+        <v>6791358</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466739</v>
+        <v>124466776</v>
       </c>
       <c r="B7" t="n">
-        <v>94959</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455032</v>
+        <v>454967</v>
       </c>
       <c r="R7" t="n">
-        <v>6791410</v>
+        <v>6791549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466785</v>
+        <v>124466758</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,31 +1319,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455002</v>
+        <v>454965</v>
       </c>
       <c r="R8" t="n">
-        <v>6791543</v>
+        <v>6791575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466741</v>
+        <v>124466745</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,7 +1453,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454985</v>
+        <v>454974</v>
       </c>
       <c r="R9" t="n">
-        <v>6791568</v>
+        <v>6791602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466771</v>
+        <v>124466761</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,38 +1541,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455011</v>
+        <v>454973</v>
       </c>
       <c r="R10" t="n">
-        <v>6791455</v>
+        <v>6791596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466717</v>
+        <v>124466743</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,38 +1652,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455070</v>
+        <v>454986</v>
       </c>
       <c r="R11" t="n">
-        <v>6791371</v>
+        <v>6791588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466774</v>
+        <v>124466763</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455009</v>
+        <v>455022</v>
       </c>
       <c r="R12" t="n">
-        <v>6791499</v>
+        <v>6791480</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466728</v>
+        <v>124466720</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,25 +1865,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454980</v>
+        <v>455013</v>
       </c>
       <c r="R13" t="n">
-        <v>6791584</v>
+        <v>6791456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466776</v>
+        <v>124466741</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,38 +1967,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454967</v>
+        <v>454985</v>
       </c>
       <c r="R14" t="n">
-        <v>6791549</v>
+        <v>6791568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466777</v>
+        <v>124466738</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,25 +2078,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2084,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454993</v>
+        <v>454961</v>
       </c>
       <c r="R15" t="n">
-        <v>6791588</v>
+        <v>6791550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466727</v>
+        <v>124466777</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454951</v>
+        <v>454993</v>
       </c>
       <c r="R16" t="n">
-        <v>6791583</v>
+        <v>6791588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466716</v>
+        <v>124466717</v>
       </c>
       <c r="B17" t="n">
         <v>90977</v>
@@ -2288,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455041</v>
+        <v>455070</v>
       </c>
       <c r="R17" t="n">
-        <v>6791358</v>
+        <v>6791371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466720</v>
+        <v>124466774</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,25 +2384,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455013</v>
+        <v>455009</v>
       </c>
       <c r="R18" t="n">
-        <v>6791456</v>
+        <v>6791499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466754</v>
+        <v>124466765</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,47 +2486,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454972</v>
+        <v>455018</v>
       </c>
       <c r="R19" t="n">
-        <v>6791550</v>
+        <v>6791399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466724</v>
+        <v>124466754</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,38 +2588,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455029</v>
+        <v>454972</v>
       </c>
       <c r="R20" t="n">
-        <v>6791510</v>
+        <v>6791550</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466725</v>
+        <v>124466713</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2705,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454951</v>
+        <v>454998</v>
       </c>
       <c r="R21" t="n">
-        <v>6791581</v>
+        <v>6791464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466763</v>
+        <v>124466723</v>
       </c>
       <c r="B22" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2807,10 +2829,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455022</v>
+        <v>455035</v>
       </c>
       <c r="R22" t="n">
-        <v>6791480</v>
+        <v>6791359</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466758</v>
+        <v>124466719</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,47 +2903,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454965</v>
+        <v>455046</v>
       </c>
       <c r="R23" t="n">
-        <v>6791575</v>
+        <v>6791403</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2993,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466743</v>
+        <v>124466756</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3015,7 +3028,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3029,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454986</v>
+        <v>454999</v>
       </c>
       <c r="R24" t="n">
-        <v>6791588</v>
+        <v>6791433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,7 +3104,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466756</v>
+        <v>124466753</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3126,7 +3139,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3140,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454999</v>
+        <v>454960</v>
       </c>
       <c r="R25" t="n">
-        <v>6791433</v>
+        <v>6791599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466719</v>
+        <v>124466787</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,38 +3338,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455046</v>
+        <v>455074</v>
       </c>
       <c r="R27" t="n">
-        <v>6791403</v>
+        <v>6791202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3389,6 +3407,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3527,7 +3550,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466751</v>
+        <v>124466740</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3562,7 +3585,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3576,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454956</v>
+        <v>455036</v>
       </c>
       <c r="R29" t="n">
-        <v>6791586</v>
+        <v>6791428</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3638,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466713</v>
+        <v>124466728</v>
       </c>
       <c r="B30" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454998</v>
+        <v>454980</v>
       </c>
       <c r="R30" t="n">
-        <v>6791464</v>
+        <v>6791584</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466753</v>
+        <v>124466739</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,47 +3775,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454960</v>
+        <v>455032</v>
       </c>
       <c r="R31" t="n">
-        <v>6791599</v>
+        <v>6791410</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3851,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466765</v>
+        <v>124466725</v>
       </c>
       <c r="B32" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3867,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455018</v>
+        <v>454951</v>
       </c>
       <c r="R32" t="n">
-        <v>6791399</v>
+        <v>6791581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466723</v>
+        <v>124466721</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3965,25 +3979,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3993,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455035</v>
+        <v>454980</v>
       </c>
       <c r="R33" t="n">
-        <v>6791359</v>
+        <v>6791584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4055,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466718</v>
+        <v>124466746</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4067,38 +4081,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455062</v>
+        <v>454971</v>
       </c>
       <c r="R34" t="n">
-        <v>6791378</v>
+        <v>6791601</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466787</v>
+        <v>124466727</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,39 +4196,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455074</v>
+        <v>454951</v>
       </c>
       <c r="R35" t="n">
-        <v>6791202</v>
+        <v>6791583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,11 +4256,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466721</v>
+        <v>124466785</v>
       </c>
       <c r="B36" t="n">
-        <v>91361</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,38 +4294,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454980</v>
+        <v>455002</v>
       </c>
       <c r="R36" t="n">
-        <v>6791584</v>
+        <v>6791543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,10 +4389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466734</v>
+        <v>124466757</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4383,31 +4401,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4416,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455027</v>
+        <v>454954</v>
       </c>
       <c r="R37" t="n">
-        <v>6791520</v>
+        <v>6791589</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4478,7 +4500,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466775</v>
+        <v>124466771</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4518,10 +4540,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454990</v>
+        <v>455011</v>
       </c>
       <c r="R38" t="n">
-        <v>6791542</v>
+        <v>6791455</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466738</v>
+        <v>124466718</v>
       </c>
       <c r="B39" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,21 +4618,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454961</v>
+        <v>455062</v>
       </c>
       <c r="R39" t="n">
-        <v>6791550</v>
+        <v>6791378</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4682,10 +4704,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466740</v>
+        <v>124466775</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,47 +4716,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455036</v>
+        <v>454990</v>
       </c>
       <c r="R40" t="n">
-        <v>6791428</v>
+        <v>6791542</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,7 +4908,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466745</v>
+        <v>124466751</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4930,7 +4943,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4944,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454974</v>
+        <v>454956</v>
       </c>
       <c r="R42" t="n">
-        <v>6791602</v>
+        <v>6791586</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466746</v>
+        <v>124466724</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,47 +5031,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454971</v>
+        <v>455029</v>
       </c>
       <c r="R43" t="n">
-        <v>6791601</v>
+        <v>6791510</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466757</v>
+        <v>124466734</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,35 +5133,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454954</v>
+        <v>455027</v>
       </c>
       <c r="R44" t="n">
-        <v>6791589</v>
+        <v>6791520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124164315</v>
+        <v>124163076</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455046</v>
+        <v>455065</v>
       </c>
       <c r="R2" t="n">
-        <v>6791351</v>
+        <v>6791354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124164341</v>
+        <v>124164315</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455084</v>
+        <v>455046</v>
       </c>
       <c r="R4" t="n">
-        <v>6791213</v>
+        <v>6791351</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124163076</v>
+        <v>124164341</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455065</v>
+        <v>455084</v>
       </c>
       <c r="R5" t="n">
-        <v>6791354</v>
+        <v>6791213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466716</v>
+        <v>124466741</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1115,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455041</v>
+        <v>454985</v>
       </c>
       <c r="R6" t="n">
-        <v>6791358</v>
+        <v>6791568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466776</v>
+        <v>124466774</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1245,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454967</v>
+        <v>455009</v>
       </c>
       <c r="R7" t="n">
-        <v>6791549</v>
+        <v>6791499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466758</v>
+        <v>124466787</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,35 +1328,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454965</v>
+        <v>455074</v>
       </c>
       <c r="R8" t="n">
-        <v>6791575</v>
+        <v>6791202</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1428,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466745</v>
+        <v>124466754</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1453,7 +1463,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454974</v>
+        <v>454972</v>
       </c>
       <c r="R9" t="n">
-        <v>6791602</v>
+        <v>6791550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466761</v>
+        <v>124466743</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1564,7 +1574,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1578,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454973</v>
+        <v>454986</v>
       </c>
       <c r="R10" t="n">
-        <v>6791596</v>
+        <v>6791588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466743</v>
+        <v>124466738</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,47 +1662,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454986</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6791588</v>
+        <v>6791550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466763</v>
+        <v>124466724</v>
       </c>
       <c r="B12" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1768,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455022</v>
+        <v>455029</v>
       </c>
       <c r="R12" t="n">
-        <v>6791480</v>
+        <v>6791510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466720</v>
+        <v>124466725</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,25 +1866,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455013</v>
+        <v>454951</v>
       </c>
       <c r="R13" t="n">
-        <v>6791456</v>
+        <v>6791581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466741</v>
+        <v>124466785</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,35 +1968,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2004,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454985</v>
+        <v>455002</v>
       </c>
       <c r="R14" t="n">
-        <v>6791568</v>
+        <v>6791543</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466738</v>
+        <v>124466775</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454961</v>
+        <v>454990</v>
       </c>
       <c r="R15" t="n">
-        <v>6791550</v>
+        <v>6791542</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466777</v>
+        <v>124466730</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,34 +2181,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454993</v>
+        <v>455093</v>
       </c>
       <c r="R16" t="n">
-        <v>6791588</v>
+        <v>6791177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,6 +2246,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466717</v>
+        <v>124466718</v>
       </c>
       <c r="B17" t="n">
         <v>90977</v>
@@ -2310,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455070</v>
+        <v>455062</v>
       </c>
       <c r="R17" t="n">
-        <v>6791371</v>
+        <v>6791378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466774</v>
+        <v>124466770</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2412,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455009</v>
+        <v>454999</v>
       </c>
       <c r="R18" t="n">
-        <v>6791499</v>
+        <v>6791433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466765</v>
+        <v>124466745</v>
       </c>
       <c r="B19" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,38 +2493,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455018</v>
+        <v>454974</v>
       </c>
       <c r="R19" t="n">
-        <v>6791399</v>
+        <v>6791602</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466754</v>
+        <v>124466761</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2611,7 +2627,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2625,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454972</v>
+        <v>454973</v>
       </c>
       <c r="R20" t="n">
-        <v>6791550</v>
+        <v>6791596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466713</v>
+        <v>124466727</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454998</v>
+        <v>454951</v>
       </c>
       <c r="R21" t="n">
-        <v>6791464</v>
+        <v>6791583</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466723</v>
+        <v>124466740</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,38 +2817,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455035</v>
+        <v>455036</v>
       </c>
       <c r="R22" t="n">
-        <v>6791359</v>
+        <v>6791428</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466719</v>
+        <v>124466765</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455046</v>
+        <v>455018</v>
       </c>
       <c r="R23" t="n">
-        <v>6791403</v>
+        <v>6791399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466756</v>
+        <v>124466763</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,47 +3030,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454999</v>
+        <v>455022</v>
       </c>
       <c r="R24" t="n">
-        <v>6791433</v>
+        <v>6791480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466753</v>
+        <v>124466719</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3116,47 +3132,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454960</v>
+        <v>455046</v>
       </c>
       <c r="R25" t="n">
-        <v>6791599</v>
+        <v>6791403</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3215,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466760</v>
+        <v>124466713</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3227,47 +3234,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455024</v>
+        <v>454998</v>
       </c>
       <c r="R26" t="n">
-        <v>6791525</v>
+        <v>6791464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466787</v>
+        <v>124466728</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,39 +3340,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455074</v>
+        <v>454980</v>
       </c>
       <c r="R27" t="n">
-        <v>6791202</v>
+        <v>6791584</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466730</v>
+        <v>124466746</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,31 +3438,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3483,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455093</v>
+        <v>454971</v>
       </c>
       <c r="R28" t="n">
-        <v>6791177</v>
+        <v>6791601</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,11 +3511,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3550,7 +3537,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466740</v>
+        <v>124466756</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3585,7 +3572,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3599,10 +3586,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455036</v>
+        <v>454999</v>
       </c>
       <c r="R29" t="n">
-        <v>6791428</v>
+        <v>6791433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466728</v>
+        <v>124466739</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>94959</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3673,25 +3660,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454980</v>
+        <v>455032</v>
       </c>
       <c r="R30" t="n">
-        <v>6791584</v>
+        <v>6791410</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,10 +3750,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466739</v>
+        <v>124466716</v>
       </c>
       <c r="B31" t="n">
-        <v>94959</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,21 +3766,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2387</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455032</v>
+        <v>455041</v>
       </c>
       <c r="R31" t="n">
-        <v>6791410</v>
+        <v>6791358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466725</v>
+        <v>124466771</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3868,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3892,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454951</v>
+        <v>455011</v>
       </c>
       <c r="R32" t="n">
-        <v>6791581</v>
+        <v>6791455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466721</v>
+        <v>124466734</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,38 +3966,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454980</v>
+        <v>455027</v>
       </c>
       <c r="R33" t="n">
-        <v>6791584</v>
+        <v>6791520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4061,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466746</v>
+        <v>124466721</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,43 +4077,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454971</v>
+        <v>454980</v>
       </c>
       <c r="R34" t="n">
-        <v>6791601</v>
+        <v>6791584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466727</v>
+        <v>124466717</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,25 +4175,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4203,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454951</v>
+        <v>455070</v>
       </c>
       <c r="R35" t="n">
-        <v>6791583</v>
+        <v>6791371</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,10 +4265,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466785</v>
+        <v>124466757</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,31 +4277,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4327,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455002</v>
+        <v>454954</v>
       </c>
       <c r="R36" t="n">
-        <v>6791543</v>
+        <v>6791589</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4389,7 +4376,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466757</v>
+        <v>124466751</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4424,7 +4411,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4438,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454954</v>
+        <v>454956</v>
       </c>
       <c r="R37" t="n">
-        <v>6791589</v>
+        <v>6791586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466771</v>
+        <v>124466758</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4512,38 +4499,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455011</v>
+        <v>454965</v>
       </c>
       <c r="R38" t="n">
-        <v>6791455</v>
+        <v>6791575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466718</v>
+        <v>124466720</v>
       </c>
       <c r="B39" t="n">
         <v>90977</v>
@@ -4642,10 +4638,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455062</v>
+        <v>455013</v>
       </c>
       <c r="R39" t="n">
-        <v>6791378</v>
+        <v>6791456</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4700,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466775</v>
+        <v>124466777</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4744,10 +4740,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454990</v>
+        <v>454993</v>
       </c>
       <c r="R40" t="n">
-        <v>6791542</v>
+        <v>6791588</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,10 +4802,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466770</v>
+        <v>124466753</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,38 +4814,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454999</v>
+        <v>454960</v>
       </c>
       <c r="R41" t="n">
-        <v>6791433</v>
+        <v>6791599</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466751</v>
+        <v>124466760</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4943,7 +4948,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4957,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454956</v>
+        <v>455024</v>
       </c>
       <c r="R42" t="n">
-        <v>6791586</v>
+        <v>6791525</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466724</v>
+        <v>124466776</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5040,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455029</v>
+        <v>454967</v>
       </c>
       <c r="R43" t="n">
-        <v>6791510</v>
+        <v>6791549</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5121,10 +5126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466734</v>
+        <v>124466723</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,39 +5142,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455027</v>
+        <v>455035</v>
       </c>
       <c r="R44" t="n">
-        <v>6791520</v>
+        <v>6791359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124163076</v>
+        <v>124164341</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455065</v>
+        <v>455084</v>
       </c>
       <c r="R2" t="n">
-        <v>6791354</v>
+        <v>6791213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124164315</v>
+        <v>124163076</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455046</v>
+        <v>455065</v>
       </c>
       <c r="R4" t="n">
-        <v>6791351</v>
+        <v>6791354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124164341</v>
+        <v>124164315</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455084</v>
+        <v>455046</v>
       </c>
       <c r="R5" t="n">
-        <v>6791213</v>
+        <v>6791351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466741</v>
+        <v>124466756</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454985</v>
+        <v>454999</v>
       </c>
       <c r="R6" t="n">
-        <v>6791568</v>
+        <v>6791433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466774</v>
+        <v>124466716</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455009</v>
+        <v>455041</v>
       </c>
       <c r="R7" t="n">
-        <v>6791499</v>
+        <v>6791358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466787</v>
+        <v>124466760</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,31 +1328,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1361,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455074</v>
+        <v>455024</v>
       </c>
       <c r="R8" t="n">
-        <v>6791202</v>
+        <v>6791525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1401,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466754</v>
+        <v>124466776</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,47 +1439,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454972</v>
+        <v>454967</v>
       </c>
       <c r="R9" t="n">
-        <v>6791550</v>
+        <v>6791549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466743</v>
+        <v>124466770</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,47 +1541,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454986</v>
+        <v>454999</v>
       </c>
       <c r="R10" t="n">
-        <v>6791588</v>
+        <v>6791433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466738</v>
+        <v>124466724</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,25 +1643,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>455029</v>
       </c>
       <c r="R11" t="n">
-        <v>6791550</v>
+        <v>6791510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466724</v>
+        <v>124466757</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1745,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455029</v>
+        <v>454954</v>
       </c>
       <c r="R12" t="n">
-        <v>6791510</v>
+        <v>6791589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466725</v>
+        <v>124466719</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454951</v>
+        <v>455046</v>
       </c>
       <c r="R13" t="n">
-        <v>6791581</v>
+        <v>6791403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466785</v>
+        <v>124466725</v>
       </c>
       <c r="B14" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,43 +1958,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455002</v>
+        <v>454951</v>
       </c>
       <c r="R14" t="n">
-        <v>6791543</v>
+        <v>6791581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2048,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466775</v>
+        <v>124466777</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2103,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454990</v>
+        <v>454993</v>
       </c>
       <c r="R15" t="n">
-        <v>6791542</v>
+        <v>6791588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466730</v>
+        <v>124466751</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,31 +2162,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2210,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455093</v>
+        <v>454956</v>
       </c>
       <c r="R16" t="n">
-        <v>6791177</v>
+        <v>6791586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,11 +2235,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466718</v>
+        <v>124466754</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,38 +2273,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455062</v>
+        <v>454972</v>
       </c>
       <c r="R17" t="n">
-        <v>6791378</v>
+        <v>6791550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466770</v>
+        <v>124466743</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,38 +2384,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454999</v>
+        <v>454986</v>
       </c>
       <c r="R18" t="n">
-        <v>6791433</v>
+        <v>6791588</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466745</v>
+        <v>124466738</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,47 +2495,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454974</v>
+        <v>454961</v>
       </c>
       <c r="R19" t="n">
-        <v>6791602</v>
+        <v>6791550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466761</v>
+        <v>124466718</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,47 +2597,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454973</v>
+        <v>455062</v>
       </c>
       <c r="R20" t="n">
-        <v>6791596</v>
+        <v>6791378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466727</v>
+        <v>124466730</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,34 +2703,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454951</v>
+        <v>455093</v>
       </c>
       <c r="R21" t="n">
-        <v>6791583</v>
+        <v>6791177</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,6 +2768,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2799,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466740</v>
+        <v>124466753</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2840,7 +2834,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2854,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455036</v>
+        <v>454960</v>
       </c>
       <c r="R22" t="n">
-        <v>6791428</v>
+        <v>6791599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466765</v>
+        <v>124466771</v>
       </c>
       <c r="B23" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2932,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455018</v>
+        <v>455011</v>
       </c>
       <c r="R23" t="n">
-        <v>6791399</v>
+        <v>6791455</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466763</v>
+        <v>124466787</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,34 +3028,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455022</v>
+        <v>455074</v>
       </c>
       <c r="R24" t="n">
-        <v>6791480</v>
+        <v>6791202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,6 +3093,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466719</v>
+        <v>124466713</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,25 +3136,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3160,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455046</v>
+        <v>454998</v>
       </c>
       <c r="R25" t="n">
-        <v>6791403</v>
+        <v>6791464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466713</v>
+        <v>124466740</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,38 +3238,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454998</v>
+        <v>455036</v>
       </c>
       <c r="R26" t="n">
-        <v>6791464</v>
+        <v>6791428</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466728</v>
+        <v>124466739</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>94959</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,25 +3349,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454980</v>
+        <v>455032</v>
       </c>
       <c r="R27" t="n">
-        <v>6791584</v>
+        <v>6791410</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466746</v>
+        <v>124466720</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,47 +3451,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454971</v>
+        <v>455013</v>
       </c>
       <c r="R28" t="n">
-        <v>6791601</v>
+        <v>6791456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3541,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466756</v>
+        <v>124466745</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3572,7 +3576,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3586,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454999</v>
+        <v>454974</v>
       </c>
       <c r="R29" t="n">
-        <v>6791433</v>
+        <v>6791602</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466739</v>
+        <v>124466761</v>
       </c>
       <c r="B30" t="n">
-        <v>94959</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,38 +3664,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455032</v>
+        <v>454973</v>
       </c>
       <c r="R30" t="n">
-        <v>6791410</v>
+        <v>6791596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466716</v>
+        <v>124466746</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3762,38 +3775,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455041</v>
+        <v>454971</v>
       </c>
       <c r="R31" t="n">
-        <v>6791358</v>
+        <v>6791601</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466771</v>
+        <v>124466717</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,25 +3886,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3892,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455011</v>
+        <v>455070</v>
       </c>
       <c r="R32" t="n">
-        <v>6791455</v>
+        <v>6791371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466734</v>
+        <v>124466775</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,39 +3992,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455027</v>
+        <v>454990</v>
       </c>
       <c r="R33" t="n">
-        <v>6791520</v>
+        <v>6791542</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466721</v>
+        <v>124466785</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>5176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,38 +4090,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454980</v>
+        <v>455002</v>
       </c>
       <c r="R34" t="n">
-        <v>6791584</v>
+        <v>6791543</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,10 +4185,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466717</v>
+        <v>124466763</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,25 +4197,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4203,10 +4225,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455070</v>
+        <v>455022</v>
       </c>
       <c r="R35" t="n">
-        <v>6791371</v>
+        <v>6791480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466757</v>
+        <v>124466727</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,47 +4299,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454954</v>
+        <v>454951</v>
       </c>
       <c r="R36" t="n">
-        <v>6791589</v>
+        <v>6791583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,10 +4389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466751</v>
+        <v>124466728</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4388,47 +4401,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454956</v>
+        <v>454980</v>
       </c>
       <c r="R37" t="n">
-        <v>6791586</v>
+        <v>6791584</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466758</v>
+        <v>124466741</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4522,7 +4526,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4536,10 +4540,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454965</v>
+        <v>454985</v>
       </c>
       <c r="R38" t="n">
-        <v>6791575</v>
+        <v>6791568</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466720</v>
+        <v>124466758</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,38 +4614,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455013</v>
+        <v>454965</v>
       </c>
       <c r="R39" t="n">
-        <v>6791456</v>
+        <v>6791575</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4713,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466777</v>
+        <v>124466721</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,25 +4725,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4740,10 +4753,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R40" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,10 +4815,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466753</v>
+        <v>124466774</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,47 +4827,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454960</v>
+        <v>455009</v>
       </c>
       <c r="R41" t="n">
-        <v>6791599</v>
+        <v>6791499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4917,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466760</v>
+        <v>124466765</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4925,47 +4929,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455024</v>
+        <v>455018</v>
       </c>
       <c r="R42" t="n">
-        <v>6791525</v>
+        <v>6791399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5024,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466776</v>
+        <v>124466723</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5040,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5059,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454967</v>
+        <v>455035</v>
       </c>
       <c r="R43" t="n">
-        <v>6791549</v>
+        <v>6791359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466723</v>
+        <v>124466734</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,34 +5137,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455035</v>
+        <v>455027</v>
       </c>
       <c r="R44" t="n">
-        <v>6791359</v>
+        <v>6791520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466756</v>
+        <v>124466716</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,47 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454999</v>
+        <v>455041</v>
       </c>
       <c r="R6" t="n">
-        <v>6791433</v>
+        <v>6791358</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466716</v>
+        <v>124466756</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,38 +1217,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455041</v>
+        <v>454999</v>
       </c>
       <c r="R7" t="n">
-        <v>6791358</v>
+        <v>6791433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466760</v>
+        <v>124466776</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,47 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455024</v>
+        <v>454967</v>
       </c>
       <c r="R8" t="n">
-        <v>6791525</v>
+        <v>6791549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466776</v>
+        <v>124466770</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1467,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454967</v>
+        <v>454999</v>
       </c>
       <c r="R9" t="n">
-        <v>6791549</v>
+        <v>6791433</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466770</v>
+        <v>124466724</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454999</v>
+        <v>455029</v>
       </c>
       <c r="R10" t="n">
-        <v>6791433</v>
+        <v>6791510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466724</v>
+        <v>124466760</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,38 +1634,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455029</v>
+        <v>455024</v>
       </c>
       <c r="R11" t="n">
-        <v>6791510</v>
+        <v>6791525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466754</v>
+        <v>124466718</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,47 +2273,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454972</v>
+        <v>455062</v>
       </c>
       <c r="R17" t="n">
-        <v>6791550</v>
+        <v>6791378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2363,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466743</v>
+        <v>124466754</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2407,7 +2398,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2421,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454986</v>
+        <v>454972</v>
       </c>
       <c r="R18" t="n">
-        <v>6791588</v>
+        <v>6791550</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466738</v>
+        <v>124466743</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,38 +2486,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454961</v>
+        <v>454986</v>
       </c>
       <c r="R19" t="n">
-        <v>6791550</v>
+        <v>6791588</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466718</v>
+        <v>124466738</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455062</v>
+        <v>454961</v>
       </c>
       <c r="R20" t="n">
-        <v>6791378</v>
+        <v>6791550</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466758</v>
+        <v>124466721</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4618,43 +4618,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454965</v>
+        <v>454980</v>
       </c>
       <c r="R39" t="n">
-        <v>6791575</v>
+        <v>6791584</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4713,10 +4704,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466721</v>
+        <v>124466774</v>
       </c>
       <c r="B40" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,25 +4716,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4753,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454980</v>
+        <v>455009</v>
       </c>
       <c r="R40" t="n">
-        <v>6791584</v>
+        <v>6791499</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4815,10 +4806,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466774</v>
+        <v>124466758</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,38 +4818,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455009</v>
+        <v>454965</v>
       </c>
       <c r="R41" t="n">
-        <v>6791499</v>
+        <v>6791575</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124162358</v>
+        <v>124164315</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455065</v>
+        <v>455046</v>
       </c>
       <c r="R3" t="n">
-        <v>6791370</v>
+        <v>6791351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124163076</v>
+        <v>124162358</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,28 +896,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
@@ -937,7 +932,7 @@
         <v>455065</v>
       </c>
       <c r="R4" t="n">
-        <v>6791354</v>
+        <v>6791370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124164315</v>
+        <v>124163076</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455046</v>
+        <v>455065</v>
       </c>
       <c r="R5" t="n">
-        <v>6791351</v>
+        <v>6791354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466716</v>
+        <v>124466771</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455041</v>
+        <v>455011</v>
       </c>
       <c r="R6" t="n">
-        <v>6791358</v>
+        <v>6791455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466756</v>
+        <v>124466776</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,47 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454999</v>
+        <v>454967</v>
       </c>
       <c r="R7" t="n">
-        <v>6791433</v>
+        <v>6791549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466776</v>
+        <v>124466719</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454967</v>
+        <v>455046</v>
       </c>
       <c r="R8" t="n">
-        <v>6791549</v>
+        <v>6791403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466770</v>
+        <v>124466728</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454999</v>
+        <v>454980</v>
       </c>
       <c r="R9" t="n">
-        <v>6791433</v>
+        <v>6791584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466724</v>
+        <v>124466734</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455029</v>
+        <v>455027</v>
       </c>
       <c r="R10" t="n">
-        <v>6791510</v>
+        <v>6791520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466760</v>
+        <v>124466743</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1671,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455024</v>
+        <v>454986</v>
       </c>
       <c r="R11" t="n">
-        <v>6791525</v>
+        <v>6791588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466757</v>
+        <v>124466754</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1768,7 +1764,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1782,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454954</v>
+        <v>454972</v>
       </c>
       <c r="R12" t="n">
-        <v>6791589</v>
+        <v>6791550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466719</v>
+        <v>124466787</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,38 +1852,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455046</v>
+        <v>455074</v>
       </c>
       <c r="R13" t="n">
-        <v>6791403</v>
+        <v>6791202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,6 +1921,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466725</v>
+        <v>124466753</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,38 +1964,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454951</v>
+        <v>454960</v>
       </c>
       <c r="R14" t="n">
-        <v>6791581</v>
+        <v>6791599</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466777</v>
+        <v>124466756</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,38 +2075,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454993</v>
+        <v>454999</v>
       </c>
       <c r="R15" t="n">
-        <v>6791588</v>
+        <v>6791433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466751</v>
+        <v>124466713</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,47 +2186,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454956</v>
+        <v>454998</v>
       </c>
       <c r="R16" t="n">
-        <v>6791586</v>
+        <v>6791464</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466718</v>
+        <v>124466751</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,38 +2288,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455062</v>
+        <v>454956</v>
       </c>
       <c r="R17" t="n">
-        <v>6791378</v>
+        <v>6791586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466754</v>
+        <v>124466716</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,47 +2399,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454972</v>
+        <v>455041</v>
       </c>
       <c r="R18" t="n">
-        <v>6791550</v>
+        <v>6791358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466743</v>
+        <v>124466724</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,47 +2501,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454986</v>
+        <v>455029</v>
       </c>
       <c r="R19" t="n">
-        <v>6791588</v>
+        <v>6791510</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466753</v>
+        <v>124466774</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,47 +2817,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454960</v>
+        <v>455009</v>
       </c>
       <c r="R22" t="n">
-        <v>6791599</v>
+        <v>6791499</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466771</v>
+        <v>124466765</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455011</v>
+        <v>455018</v>
       </c>
       <c r="R23" t="n">
-        <v>6791455</v>
+        <v>6791399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466787</v>
+        <v>124466720</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,43 +3021,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455074</v>
+        <v>455013</v>
       </c>
       <c r="R24" t="n">
-        <v>6791202</v>
+        <v>6791456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,11 +3085,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466713</v>
+        <v>124466723</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454998</v>
+        <v>455035</v>
       </c>
       <c r="R25" t="n">
-        <v>6791464</v>
+        <v>6791359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466740</v>
+        <v>124466760</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3261,7 +3248,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3275,10 +3262,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455036</v>
+        <v>455024</v>
       </c>
       <c r="R26" t="n">
-        <v>6791428</v>
+        <v>6791525</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466739</v>
+        <v>124466727</v>
       </c>
       <c r="B27" t="n">
-        <v>94959</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,25 +3336,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455032</v>
+        <v>454951</v>
       </c>
       <c r="R27" t="n">
-        <v>6791410</v>
+        <v>6791583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466720</v>
+        <v>124466770</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,25 +3438,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455013</v>
+        <v>454999</v>
       </c>
       <c r="R28" t="n">
-        <v>6791456</v>
+        <v>6791433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,7 +3528,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466745</v>
+        <v>124466741</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3576,7 +3563,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3590,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454974</v>
+        <v>454985</v>
       </c>
       <c r="R29" t="n">
-        <v>6791602</v>
+        <v>6791568</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466761</v>
+        <v>124466721</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,43 +3655,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454973</v>
+        <v>454980</v>
       </c>
       <c r="R30" t="n">
-        <v>6791596</v>
+        <v>6791584</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466746</v>
+        <v>124466739</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,47 +3753,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454971</v>
+        <v>455032</v>
       </c>
       <c r="R31" t="n">
-        <v>6791601</v>
+        <v>6791410</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3874,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466717</v>
+        <v>124466740</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,38 +3855,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455070</v>
+        <v>455036</v>
       </c>
       <c r="R32" t="n">
-        <v>6791371</v>
+        <v>6791428</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466775</v>
+        <v>124466745</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,38 +3966,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454990</v>
+        <v>454974</v>
       </c>
       <c r="R33" t="n">
-        <v>6791542</v>
+        <v>6791602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466785</v>
+        <v>124466775</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,43 +4077,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455002</v>
+        <v>454990</v>
       </c>
       <c r="R34" t="n">
-        <v>6791543</v>
+        <v>6791542</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4185,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466763</v>
+        <v>124466718</v>
       </c>
       <c r="B35" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,25 +4179,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4225,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455022</v>
+        <v>455062</v>
       </c>
       <c r="R35" t="n">
-        <v>6791480</v>
+        <v>6791378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4287,7 +4269,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466727</v>
+        <v>124466725</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4330,7 +4312,7 @@
         <v>454951</v>
       </c>
       <c r="R36" t="n">
-        <v>6791583</v>
+        <v>6791581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4389,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466728</v>
+        <v>124466785</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,38 +4383,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454980</v>
+        <v>455002</v>
       </c>
       <c r="R37" t="n">
-        <v>6791584</v>
+        <v>6791543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4491,7 +4478,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466741</v>
+        <v>124466761</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4526,7 +4513,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4540,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454985</v>
+        <v>454973</v>
       </c>
       <c r="R38" t="n">
-        <v>6791568</v>
+        <v>6791596</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466721</v>
+        <v>124466757</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4618,34 +4605,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454980</v>
+        <v>454954</v>
       </c>
       <c r="R39" t="n">
-        <v>6791584</v>
+        <v>6791589</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466774</v>
+        <v>124466758</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4716,38 +4712,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455009</v>
+        <v>454965</v>
       </c>
       <c r="R40" t="n">
-        <v>6791499</v>
+        <v>6791575</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466758</v>
+        <v>124466717</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,47 +4823,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454965</v>
+        <v>455070</v>
       </c>
       <c r="R41" t="n">
-        <v>6791575</v>
+        <v>6791371</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4917,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466765</v>
+        <v>124466763</v>
       </c>
       <c r="B42" t="n">
         <v>91026</v>
@@ -4957,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455018</v>
+        <v>455022</v>
       </c>
       <c r="R42" t="n">
-        <v>6791399</v>
+        <v>6791480</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466723</v>
+        <v>124466777</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5059,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455035</v>
+        <v>454993</v>
       </c>
       <c r="R43" t="n">
-        <v>6791359</v>
+        <v>6791588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5121,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466734</v>
+        <v>124466746</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5133,31 +5129,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455027</v>
+        <v>454971</v>
       </c>
       <c r="R44" t="n">
-        <v>6791520</v>
+        <v>6791601</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466728</v>
+        <v>124466734</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454980</v>
+        <v>455027</v>
       </c>
       <c r="R9" t="n">
-        <v>6791584</v>
+        <v>6791520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466734</v>
+        <v>124466728</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455027</v>
+        <v>454980</v>
       </c>
       <c r="R10" t="n">
-        <v>6791520</v>
+        <v>6791584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466730</v>
+        <v>124466774</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,39 +2709,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455093</v>
+        <v>455009</v>
       </c>
       <c r="R21" t="n">
-        <v>6791177</v>
+        <v>6791499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2769,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466774</v>
+        <v>124466730</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,34 +2811,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455009</v>
+        <v>455093</v>
       </c>
       <c r="R22" t="n">
-        <v>6791499</v>
+        <v>6791177</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4065,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466775</v>
+        <v>124466785</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,38 +4077,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454990</v>
+        <v>455002</v>
       </c>
       <c r="R34" t="n">
-        <v>6791542</v>
+        <v>6791543</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466718</v>
+        <v>124466775</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,25 +4184,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455062</v>
+        <v>454990</v>
       </c>
       <c r="R35" t="n">
-        <v>6791378</v>
+        <v>6791542</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466725</v>
+        <v>124466718</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,25 +4286,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454951</v>
+        <v>455062</v>
       </c>
       <c r="R36" t="n">
-        <v>6791581</v>
+        <v>6791378</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466785</v>
+        <v>124466725</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4383,43 +4388,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455002</v>
+        <v>454951</v>
       </c>
       <c r="R37" t="n">
-        <v>6791543</v>
+        <v>6791581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466776</v>
+        <v>124466728</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454967</v>
+        <v>454980</v>
       </c>
       <c r="R7" t="n">
-        <v>6791549</v>
+        <v>6791584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466719</v>
+        <v>124466776</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455046</v>
+        <v>454967</v>
       </c>
       <c r="R8" t="n">
-        <v>6791403</v>
+        <v>6791549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466734</v>
+        <v>124466719</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,43 +1421,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455027</v>
+        <v>455046</v>
       </c>
       <c r="R9" t="n">
-        <v>6791520</v>
+        <v>6791403</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466728</v>
+        <v>124466734</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454980</v>
+        <v>455027</v>
       </c>
       <c r="R10" t="n">
-        <v>6791584</v>
+        <v>6791520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466727</v>
+        <v>124466770</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454951</v>
+        <v>454999</v>
       </c>
       <c r="R27" t="n">
-        <v>6791583</v>
+        <v>6791433</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466770</v>
+        <v>124466727</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454999</v>
+        <v>454951</v>
       </c>
       <c r="R28" t="n">
-        <v>6791433</v>
+        <v>6791583</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466758</v>
+        <v>124466777</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,47 +4712,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454965</v>
+        <v>454993</v>
       </c>
       <c r="R40" t="n">
-        <v>6791575</v>
+        <v>6791588</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5015,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466777</v>
+        <v>124466758</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,38 +5018,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454993</v>
+        <v>454965</v>
       </c>
       <c r="R43" t="n">
-        <v>6791588</v>
+        <v>6791575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124164341</v>
+        <v>124164315</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455084</v>
+        <v>455046</v>
       </c>
       <c r="R2" t="n">
-        <v>6791213</v>
+        <v>6791351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124164315</v>
+        <v>124162358</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455046</v>
+        <v>455065</v>
       </c>
       <c r="R3" t="n">
-        <v>6791351</v>
+        <v>6791370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124162358</v>
+        <v>124164341</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455065</v>
+        <v>455084</v>
       </c>
       <c r="R4" t="n">
-        <v>6791370</v>
+        <v>6791213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466771</v>
+        <v>124466717</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455011</v>
+        <v>455070</v>
       </c>
       <c r="R6" t="n">
-        <v>6791455</v>
+        <v>6791371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466728</v>
+        <v>124466787</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454980</v>
+        <v>455074</v>
       </c>
       <c r="R7" t="n">
-        <v>6791584</v>
+        <v>6791202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466776</v>
+        <v>124466741</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,38 +1329,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454967</v>
+        <v>454985</v>
       </c>
       <c r="R8" t="n">
-        <v>6791549</v>
+        <v>6791568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466719</v>
+        <v>124466728</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1440,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455046</v>
+        <v>454980</v>
       </c>
       <c r="R9" t="n">
-        <v>6791403</v>
+        <v>6791584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466734</v>
+        <v>124466775</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1546,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455027</v>
+        <v>454990</v>
       </c>
       <c r="R10" t="n">
-        <v>6791520</v>
+        <v>6791542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466743</v>
+        <v>124466718</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,47 +1644,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454986</v>
+        <v>455062</v>
       </c>
       <c r="R11" t="n">
-        <v>6791588</v>
+        <v>6791378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466754</v>
+        <v>124466746</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1764,7 +1769,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1778,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454972</v>
+        <v>454971</v>
       </c>
       <c r="R12" t="n">
-        <v>6791550</v>
+        <v>6791601</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466787</v>
+        <v>124466771</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,39 +1861,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455074</v>
+        <v>455011</v>
       </c>
       <c r="R13" t="n">
-        <v>6791202</v>
+        <v>6791455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,11 +1921,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466753</v>
+        <v>124466774</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,47 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454960</v>
+        <v>455009</v>
       </c>
       <c r="R14" t="n">
-        <v>6791599</v>
+        <v>6791499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466756</v>
+        <v>124466743</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2098,7 +2084,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2112,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454999</v>
+        <v>454986</v>
       </c>
       <c r="R15" t="n">
-        <v>6791433</v>
+        <v>6791588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466713</v>
+        <v>124466765</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
+        <v>91026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2176,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454998</v>
+        <v>455018</v>
       </c>
       <c r="R16" t="n">
-        <v>6791464</v>
+        <v>6791399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466751</v>
+        <v>124466785</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2288,35 +2274,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2325,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454956</v>
+        <v>455002</v>
       </c>
       <c r="R17" t="n">
-        <v>6791586</v>
+        <v>6791543</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466716</v>
+        <v>124466754</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2399,38 +2381,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455041</v>
+        <v>454972</v>
       </c>
       <c r="R18" t="n">
-        <v>6791358</v>
+        <v>6791550</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466724</v>
+        <v>124466738</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,25 +2492,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455029</v>
+        <v>454961</v>
       </c>
       <c r="R19" t="n">
-        <v>6791510</v>
+        <v>6791550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466738</v>
+        <v>124466719</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2598,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454961</v>
+        <v>455046</v>
       </c>
       <c r="R20" t="n">
-        <v>6791550</v>
+        <v>6791403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466774</v>
+        <v>124466734</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,34 +2700,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455009</v>
+        <v>455027</v>
       </c>
       <c r="R21" t="n">
-        <v>6791499</v>
+        <v>6791520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466730</v>
+        <v>124466770</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,39 +2807,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455093</v>
+        <v>454999</v>
       </c>
       <c r="R22" t="n">
-        <v>6791177</v>
+        <v>6791433</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2867,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466765</v>
+        <v>124466713</v>
       </c>
       <c r="B23" t="n">
-        <v>91026</v>
+        <v>96354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2909,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455018</v>
+        <v>454998</v>
       </c>
       <c r="R23" t="n">
-        <v>6791399</v>
+        <v>6791464</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466723</v>
+        <v>124466756</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,38 +3109,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455035</v>
+        <v>454999</v>
       </c>
       <c r="R25" t="n">
-        <v>6791359</v>
+        <v>6791433</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466760</v>
+        <v>124466721</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,43 +3224,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455024</v>
+        <v>454980</v>
       </c>
       <c r="R26" t="n">
-        <v>6791525</v>
+        <v>6791584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466770</v>
+        <v>124466763</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3340,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454999</v>
+        <v>455022</v>
       </c>
       <c r="R27" t="n">
-        <v>6791433</v>
+        <v>6791480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466727</v>
+        <v>124466730</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3442,34 +3428,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454951</v>
+        <v>455093</v>
       </c>
       <c r="R28" t="n">
-        <v>6791583</v>
+        <v>6791177</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3502,6 +3493,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466741</v>
+        <v>124466757</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3563,7 +3559,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3577,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454985</v>
+        <v>454954</v>
       </c>
       <c r="R29" t="n">
-        <v>6791568</v>
+        <v>6791589</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466721</v>
+        <v>124466723</v>
       </c>
       <c r="B30" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3647,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454980</v>
+        <v>455035</v>
       </c>
       <c r="R30" t="n">
-        <v>6791584</v>
+        <v>6791359</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,10 +3737,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466739</v>
+        <v>124466724</v>
       </c>
       <c r="B31" t="n">
-        <v>94959</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,25 +3749,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3777,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455032</v>
+        <v>455029</v>
       </c>
       <c r="R31" t="n">
-        <v>6791410</v>
+        <v>6791510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,10 +3839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466740</v>
+        <v>124466716</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3855,47 +3851,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455036</v>
+        <v>455041</v>
       </c>
       <c r="R32" t="n">
-        <v>6791428</v>
+        <v>6791358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,7 +3941,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466745</v>
+        <v>124466751</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -3989,7 +3976,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4003,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454974</v>
+        <v>454956</v>
       </c>
       <c r="R33" t="n">
-        <v>6791602</v>
+        <v>6791586</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466785</v>
+        <v>124466740</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,31 +4064,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4110,10 +4101,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455002</v>
+        <v>455036</v>
       </c>
       <c r="R34" t="n">
-        <v>6791543</v>
+        <v>6791428</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4172,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466775</v>
+        <v>124466753</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,38 +4175,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454990</v>
+        <v>454960</v>
       </c>
       <c r="R35" t="n">
-        <v>6791542</v>
+        <v>6791599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466718</v>
+        <v>124466776</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4286,25 +4286,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455062</v>
+        <v>454967</v>
       </c>
       <c r="R36" t="n">
-        <v>6791378</v>
+        <v>6791549</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466725</v>
+        <v>124466761</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4388,38 +4388,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454951</v>
+        <v>454973</v>
       </c>
       <c r="R37" t="n">
-        <v>6791581</v>
+        <v>6791596</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4478,7 +4487,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466761</v>
+        <v>124466758</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4513,7 +4522,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4527,10 +4536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454973</v>
+        <v>454965</v>
       </c>
       <c r="R38" t="n">
-        <v>6791596</v>
+        <v>6791575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466757</v>
+        <v>124466727</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,47 +4610,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454954</v>
+        <v>454951</v>
       </c>
       <c r="R39" t="n">
-        <v>6791589</v>
+        <v>6791583</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466777</v>
+        <v>124466725</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454993</v>
+        <v>454951</v>
       </c>
       <c r="R40" t="n">
-        <v>6791588</v>
+        <v>6791581</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466717</v>
+        <v>124466777</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,25 +4814,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455070</v>
+        <v>454993</v>
       </c>
       <c r="R41" t="n">
-        <v>6791371</v>
+        <v>6791588</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466763</v>
+        <v>124466739</v>
       </c>
       <c r="B42" t="n">
-        <v>91026</v>
+        <v>94959</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,25 +4916,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>2387</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455022</v>
+        <v>455032</v>
       </c>
       <c r="R42" t="n">
-        <v>6791480</v>
+        <v>6791410</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466758</v>
+        <v>124466745</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454965</v>
+        <v>454974</v>
       </c>
       <c r="R43" t="n">
-        <v>6791575</v>
+        <v>6791602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466746</v>
+        <v>124466760</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454971</v>
+        <v>455024</v>
       </c>
       <c r="R44" t="n">
-        <v>6791601</v>
+        <v>6791525</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124164315</v>
+        <v>124164341</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455046</v>
+        <v>455084</v>
       </c>
       <c r="R2" t="n">
-        <v>6791351</v>
+        <v>6791213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124162358</v>
+        <v>124163076</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,33 +794,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
@@ -825,7 +825,7 @@
         <v>455065</v>
       </c>
       <c r="R3" t="n">
-        <v>6791370</v>
+        <v>6791354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124164341</v>
+        <v>124162358</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455084</v>
+        <v>455065</v>
       </c>
       <c r="R4" t="n">
-        <v>6791213</v>
+        <v>6791370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124163076</v>
+        <v>124164315</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455065</v>
+        <v>455046</v>
       </c>
       <c r="R5" t="n">
-        <v>6791354</v>
+        <v>6791351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466717</v>
+        <v>124466776</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455070</v>
+        <v>454967</v>
       </c>
       <c r="R6" t="n">
-        <v>6791371</v>
+        <v>6791549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466787</v>
+        <v>124466728</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455074</v>
+        <v>454980</v>
       </c>
       <c r="R7" t="n">
-        <v>6791202</v>
+        <v>6791584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466741</v>
+        <v>124466716</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,47 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454985</v>
+        <v>455041</v>
       </c>
       <c r="R8" t="n">
-        <v>6791568</v>
+        <v>6791358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466728</v>
+        <v>124466724</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1468,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454980</v>
+        <v>455029</v>
       </c>
       <c r="R9" t="n">
-        <v>6791584</v>
+        <v>6791510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466775</v>
+        <v>124466717</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454990</v>
+        <v>455070</v>
       </c>
       <c r="R10" t="n">
-        <v>6791542</v>
+        <v>6791371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466718</v>
+        <v>124466734</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,38 +1625,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455062</v>
+        <v>455027</v>
       </c>
       <c r="R11" t="n">
-        <v>6791378</v>
+        <v>6791520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466746</v>
+        <v>124466775</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,47 +1732,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454971</v>
+        <v>454990</v>
       </c>
       <c r="R12" t="n">
-        <v>6791601</v>
+        <v>6791542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466771</v>
+        <v>124466758</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,38 +1834,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455011</v>
+        <v>454965</v>
       </c>
       <c r="R13" t="n">
-        <v>6791455</v>
+        <v>6791575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466774</v>
+        <v>124466770</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1987,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455009</v>
+        <v>454999</v>
       </c>
       <c r="R14" t="n">
-        <v>6791499</v>
+        <v>6791433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466743</v>
+        <v>124466718</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,47 +2047,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454986</v>
+        <v>455062</v>
       </c>
       <c r="R15" t="n">
-        <v>6791588</v>
+        <v>6791378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466765</v>
+        <v>124466761</v>
       </c>
       <c r="B16" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,38 +2149,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455018</v>
+        <v>454973</v>
       </c>
       <c r="R16" t="n">
-        <v>6791399</v>
+        <v>6791596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466785</v>
+        <v>124466741</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,31 +2260,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2307,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455002</v>
+        <v>454985</v>
       </c>
       <c r="R17" t="n">
-        <v>6791543</v>
+        <v>6791568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2359,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466754</v>
+        <v>124466756</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2404,7 +2394,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2418,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454972</v>
+        <v>454999</v>
       </c>
       <c r="R18" t="n">
-        <v>6791550</v>
+        <v>6791433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466738</v>
+        <v>124466785</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,34 +2486,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454961</v>
+        <v>455002</v>
       </c>
       <c r="R19" t="n">
-        <v>6791550</v>
+        <v>6791543</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466719</v>
+        <v>124466774</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2594,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455046</v>
+        <v>455009</v>
       </c>
       <c r="R20" t="n">
-        <v>6791403</v>
+        <v>6791499</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466734</v>
+        <v>124466751</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,31 +2691,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2729,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455027</v>
+        <v>454956</v>
       </c>
       <c r="R21" t="n">
-        <v>6791520</v>
+        <v>6791586</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466770</v>
+        <v>124466720</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2803,25 +2802,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454999</v>
+        <v>455013</v>
       </c>
       <c r="R22" t="n">
-        <v>6791433</v>
+        <v>6791456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466713</v>
+        <v>124466777</v>
       </c>
       <c r="B23" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2909,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2933,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454998</v>
+        <v>454993</v>
       </c>
       <c r="R23" t="n">
-        <v>6791464</v>
+        <v>6791588</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466720</v>
+        <v>124466738</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3035,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455013</v>
+        <v>454961</v>
       </c>
       <c r="R24" t="n">
-        <v>6791456</v>
+        <v>6791550</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466756</v>
+        <v>124466760</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3132,7 +3131,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3146,10 +3145,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454999</v>
+        <v>455024</v>
       </c>
       <c r="R25" t="n">
-        <v>6791433</v>
+        <v>6791525</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466721</v>
+        <v>124466763</v>
       </c>
       <c r="B26" t="n">
-        <v>91361</v>
+        <v>91026</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454980</v>
+        <v>455022</v>
       </c>
       <c r="R26" t="n">
-        <v>6791584</v>
+        <v>6791480</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466763</v>
+        <v>124466725</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,21 +3325,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455022</v>
+        <v>454951</v>
       </c>
       <c r="R27" t="n">
-        <v>6791480</v>
+        <v>6791581</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466730</v>
+        <v>124466740</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,31 +3423,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3457,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455093</v>
+        <v>455036</v>
       </c>
       <c r="R28" t="n">
-        <v>6791177</v>
+        <v>6791428</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,11 +3496,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,7 +3522,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466757</v>
+        <v>124466746</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3559,7 +3557,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3573,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454954</v>
+        <v>454971</v>
       </c>
       <c r="R29" t="n">
-        <v>6791589</v>
+        <v>6791601</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466723</v>
+        <v>124466765</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,21 +3649,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3675,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455035</v>
+        <v>455018</v>
       </c>
       <c r="R30" t="n">
-        <v>6791359</v>
+        <v>6791399</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466724</v>
+        <v>124466745</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,38 +3747,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455029</v>
+        <v>454974</v>
       </c>
       <c r="R31" t="n">
-        <v>6791510</v>
+        <v>6791602</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466716</v>
+        <v>124466723</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3879,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455041</v>
+        <v>455035</v>
       </c>
       <c r="R32" t="n">
-        <v>6791358</v>
+        <v>6791359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466751</v>
+        <v>124466727</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,47 +3960,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454956</v>
+        <v>454951</v>
       </c>
       <c r="R33" t="n">
-        <v>6791586</v>
+        <v>6791583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,7 +4050,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466740</v>
+        <v>124466743</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4101,10 +4099,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455036</v>
+        <v>454986</v>
       </c>
       <c r="R34" t="n">
-        <v>6791428</v>
+        <v>6791588</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466753</v>
+        <v>124466730</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,35 +4173,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4212,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454960</v>
+        <v>455093</v>
       </c>
       <c r="R35" t="n">
-        <v>6791599</v>
+        <v>6791177</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4242,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466776</v>
+        <v>124466787</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4290,34 +4289,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454967</v>
+        <v>455074</v>
       </c>
       <c r="R36" t="n">
-        <v>6791549</v>
+        <v>6791202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,6 +4354,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466761</v>
+        <v>124466754</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4411,7 +4420,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4425,10 +4434,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454973</v>
+        <v>454972</v>
       </c>
       <c r="R37" t="n">
-        <v>6791596</v>
+        <v>6791550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4496,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466758</v>
+        <v>124466771</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,47 +4508,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454965</v>
+        <v>455011</v>
       </c>
       <c r="R38" t="n">
-        <v>6791575</v>
+        <v>6791455</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466727</v>
+        <v>124466721</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,25 +4610,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454951</v>
+        <v>454980</v>
       </c>
       <c r="R39" t="n">
-        <v>6791583</v>
+        <v>6791584</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466725</v>
+        <v>124466753</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,38 +4712,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454951</v>
+        <v>454960</v>
       </c>
       <c r="R40" t="n">
-        <v>6791581</v>
+        <v>6791599</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466777</v>
+        <v>124466757</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,38 +4823,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454993</v>
+        <v>454954</v>
       </c>
       <c r="R41" t="n">
-        <v>6791588</v>
+        <v>6791589</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4922,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466739</v>
+        <v>124466713</v>
       </c>
       <c r="B42" t="n">
-        <v>94959</v>
+        <v>96354</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,25 +4934,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2387</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4944,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455032</v>
+        <v>454998</v>
       </c>
       <c r="R42" t="n">
-        <v>6791410</v>
+        <v>6791464</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,10 +5024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466745</v>
+        <v>124466739</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,47 +5036,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454974</v>
+        <v>455032</v>
       </c>
       <c r="R43" t="n">
-        <v>6791602</v>
+        <v>6791410</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,10 +5126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466760</v>
+        <v>124466719</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,47 +5138,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455024</v>
+        <v>455046</v>
       </c>
       <c r="R44" t="n">
-        <v>6791525</v>
+        <v>6791403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466774</v>
+        <v>124466720</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455009</v>
+        <v>455013</v>
       </c>
       <c r="R20" t="n">
-        <v>6791499</v>
+        <v>6791456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466720</v>
+        <v>124466774</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,25 +2802,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455013</v>
+        <v>455009</v>
       </c>
       <c r="R22" t="n">
-        <v>6791456</v>
+        <v>6791499</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466777</v>
+        <v>124466760</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,38 +2904,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454993</v>
+        <v>455024</v>
       </c>
       <c r="R23" t="n">
-        <v>6791588</v>
+        <v>6791525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466738</v>
+        <v>124466763</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,25 +3015,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454961</v>
+        <v>455022</v>
       </c>
       <c r="R24" t="n">
-        <v>6791550</v>
+        <v>6791480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466760</v>
+        <v>124466777</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,47 +3117,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455024</v>
+        <v>454993</v>
       </c>
       <c r="R25" t="n">
-        <v>6791525</v>
+        <v>6791588</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466763</v>
+        <v>124466738</v>
       </c>
       <c r="B26" t="n">
-        <v>91026</v>
+        <v>96979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455022</v>
+        <v>454961</v>
       </c>
       <c r="R26" t="n">
-        <v>6791480</v>
+        <v>6791550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466745</v>
+        <v>124466723</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,47 +3747,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454974</v>
+        <v>455035</v>
       </c>
       <c r="R31" t="n">
-        <v>6791602</v>
+        <v>6791359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466723</v>
+        <v>124466727</v>
       </c>
       <c r="B32" t="n">
         <v>91012</v>
@@ -3886,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455035</v>
+        <v>454951</v>
       </c>
       <c r="R32" t="n">
-        <v>6791359</v>
+        <v>6791583</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466727</v>
+        <v>124466745</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,38 +3951,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454951</v>
+        <v>454974</v>
       </c>
       <c r="R33" t="n">
-        <v>6791583</v>
+        <v>6791602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124164341</v>
+        <v>124164315</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455084</v>
+        <v>455046</v>
       </c>
       <c r="R2" t="n">
-        <v>6791213</v>
+        <v>6791351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124163076</v>
+        <v>124162358</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,28 +789,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
@@ -825,7 +825,7 @@
         <v>455065</v>
       </c>
       <c r="R3" t="n">
-        <v>6791354</v>
+        <v>6791370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124162358</v>
+        <v>124163076</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,33 +901,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjuränden, Dlr</t>
@@ -937,7 +932,7 @@
         <v>455065</v>
       </c>
       <c r="R4" t="n">
-        <v>6791370</v>
+        <v>6791354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbilder. Källa i närområdet av hackspåret samt bilder för området.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124164315</v>
+        <v>124164341</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455046</v>
+        <v>455084</v>
       </c>
       <c r="R5" t="n">
-        <v>6791351</v>
+        <v>6791213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466776</v>
+        <v>124466757</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1115,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454967</v>
+        <v>454954</v>
       </c>
       <c r="R6" t="n">
-        <v>6791549</v>
+        <v>6791589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466728</v>
+        <v>124466765</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454980</v>
+        <v>455018</v>
       </c>
       <c r="R7" t="n">
-        <v>6791584</v>
+        <v>6791399</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466716</v>
+        <v>124466777</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455041</v>
+        <v>454993</v>
       </c>
       <c r="R8" t="n">
-        <v>6791358</v>
+        <v>6791588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466724</v>
+        <v>124466727</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1449,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455029</v>
+        <v>454951</v>
       </c>
       <c r="R9" t="n">
-        <v>6791510</v>
+        <v>6791583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466717</v>
+        <v>124466719</v>
       </c>
       <c r="B10" t="n">
         <v>90977</v>
@@ -1551,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455070</v>
+        <v>455046</v>
       </c>
       <c r="R10" t="n">
-        <v>6791371</v>
+        <v>6791403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466734</v>
+        <v>124466760</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,31 +1634,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455027</v>
+        <v>455024</v>
       </c>
       <c r="R11" t="n">
-        <v>6791520</v>
+        <v>6791525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466775</v>
+        <v>124466743</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,38 +1745,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454990</v>
+        <v>454986</v>
       </c>
       <c r="R12" t="n">
-        <v>6791542</v>
+        <v>6791588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466758</v>
+        <v>124466739</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,47 +1856,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454965</v>
+        <v>455032</v>
       </c>
       <c r="R13" t="n">
-        <v>6791575</v>
+        <v>6791410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466770</v>
+        <v>124466758</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,38 +1958,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454999</v>
+        <v>454965</v>
       </c>
       <c r="R14" t="n">
-        <v>6791433</v>
+        <v>6791575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466718</v>
+        <v>124466713</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2075,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455062</v>
+        <v>454998</v>
       </c>
       <c r="R15" t="n">
-        <v>6791378</v>
+        <v>6791464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466761</v>
+        <v>124466763</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,47 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454973</v>
+        <v>455022</v>
       </c>
       <c r="R16" t="n">
-        <v>6791596</v>
+        <v>6791480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466741</v>
+        <v>124466723</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,47 +2273,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454985</v>
+        <v>455035</v>
       </c>
       <c r="R17" t="n">
-        <v>6791568</v>
+        <v>6791359</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466756</v>
+        <v>124466724</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,47 +2375,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454999</v>
+        <v>455029</v>
       </c>
       <c r="R18" t="n">
-        <v>6791433</v>
+        <v>6791510</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466785</v>
+        <v>124466725</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,43 +2477,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455002</v>
+        <v>454951</v>
       </c>
       <c r="R19" t="n">
-        <v>6791543</v>
+        <v>6791581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2567,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466720</v>
+        <v>124466718</v>
       </c>
       <c r="B20" t="n">
         <v>90977</v>
@@ -2617,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455013</v>
+        <v>455062</v>
       </c>
       <c r="R20" t="n">
-        <v>6791456</v>
+        <v>6791378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,7 +2669,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466751</v>
+        <v>124466756</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2714,7 +2704,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2728,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454956</v>
+        <v>454999</v>
       </c>
       <c r="R21" t="n">
-        <v>6791586</v>
+        <v>6791433</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466774</v>
+        <v>124466775</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2830,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455009</v>
+        <v>454990</v>
       </c>
       <c r="R22" t="n">
-        <v>6791499</v>
+        <v>6791542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466760</v>
+        <v>124466716</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,47 +2894,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455024</v>
+        <v>455041</v>
       </c>
       <c r="R23" t="n">
-        <v>6791525</v>
+        <v>6791358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466763</v>
+        <v>124466745</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,38 +2996,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455022</v>
+        <v>454974</v>
       </c>
       <c r="R24" t="n">
-        <v>6791480</v>
+        <v>6791602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466777</v>
+        <v>124466721</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,25 +3107,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3145,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R25" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466738</v>
+        <v>124466753</v>
       </c>
       <c r="B26" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,38 +3209,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454961</v>
+        <v>454960</v>
       </c>
       <c r="R26" t="n">
-        <v>6791550</v>
+        <v>6791599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466725</v>
+        <v>124466740</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,38 +3320,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454951</v>
+        <v>455036</v>
       </c>
       <c r="R27" t="n">
-        <v>6791581</v>
+        <v>6791428</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,7 +3419,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466740</v>
+        <v>124466746</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3446,7 +3454,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3460,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455036</v>
+        <v>454971</v>
       </c>
       <c r="R28" t="n">
-        <v>6791428</v>
+        <v>6791601</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466746</v>
+        <v>124466720</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3534,47 +3542,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454971</v>
+        <v>455013</v>
       </c>
       <c r="R29" t="n">
-        <v>6791601</v>
+        <v>6791456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466765</v>
+        <v>124466770</v>
       </c>
       <c r="B30" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3673,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455018</v>
+        <v>454999</v>
       </c>
       <c r="R30" t="n">
-        <v>6791399</v>
+        <v>6791433</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466723</v>
+        <v>124466776</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,21 +3750,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3774,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455035</v>
+        <v>454967</v>
       </c>
       <c r="R31" t="n">
-        <v>6791359</v>
+        <v>6791549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3836,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466727</v>
+        <v>124466751</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,38 +3848,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454951</v>
+        <v>454956</v>
       </c>
       <c r="R32" t="n">
-        <v>6791583</v>
+        <v>6791586</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466745</v>
+        <v>124466728</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,47 +3959,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454974</v>
+        <v>454980</v>
       </c>
       <c r="R33" t="n">
-        <v>6791602</v>
+        <v>6791584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466743</v>
+        <v>124466771</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,47 +4061,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454986</v>
+        <v>455011</v>
       </c>
       <c r="R34" t="n">
-        <v>6791588</v>
+        <v>6791455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466730</v>
+        <v>124466734</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4177,16 +4167,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4197,7 +4187,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4206,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455093</v>
+        <v>455027</v>
       </c>
       <c r="R35" t="n">
-        <v>6791177</v>
+        <v>6791520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4242,11 +4232,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466787</v>
+        <v>124466754</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4285,31 +4270,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4318,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455074</v>
+        <v>454972</v>
       </c>
       <c r="R36" t="n">
-        <v>6791202</v>
+        <v>6791550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,11 +4343,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4369,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466754</v>
+        <v>124466761</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4420,7 +4404,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4434,10 +4418,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454972</v>
+        <v>454973</v>
       </c>
       <c r="R37" t="n">
-        <v>6791550</v>
+        <v>6791596</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,10 +4480,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466771</v>
+        <v>124466717</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,25 +4492,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4536,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455011</v>
+        <v>455070</v>
       </c>
       <c r="R38" t="n">
-        <v>6791455</v>
+        <v>6791371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4582,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466721</v>
+        <v>124466785</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>5176</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,38 +4594,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454980</v>
+        <v>455002</v>
       </c>
       <c r="R39" t="n">
-        <v>6791584</v>
+        <v>6791543</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466753</v>
+        <v>124466730</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,35 +4701,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4749,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454960</v>
+        <v>455093</v>
       </c>
       <c r="R40" t="n">
-        <v>6791599</v>
+        <v>6791177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,6 +4770,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466757</v>
+        <v>124466738</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,47 +4813,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454954</v>
+        <v>454961</v>
       </c>
       <c r="R41" t="n">
-        <v>6791589</v>
+        <v>6791550</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4922,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466713</v>
+        <v>124466787</v>
       </c>
       <c r="B42" t="n">
-        <v>96354</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4938,34 +4919,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454998</v>
+        <v>455074</v>
       </c>
       <c r="R42" t="n">
-        <v>6791464</v>
+        <v>6791202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4998,6 +4984,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5024,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466739</v>
+        <v>124466741</v>
       </c>
       <c r="B43" t="n">
-        <v>94959</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,38 +5027,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455032</v>
+        <v>454985</v>
       </c>
       <c r="R43" t="n">
-        <v>6791410</v>
+        <v>6791568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466719</v>
+        <v>124466774</v>
       </c>
       <c r="B44" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,25 +5138,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455046</v>
+        <v>455009</v>
       </c>
       <c r="R44" t="n">
-        <v>6791403</v>
+        <v>6791499</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -2567,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466718</v>
+        <v>124466756</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,38 +2579,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455062</v>
+        <v>454999</v>
       </c>
       <c r="R20" t="n">
-        <v>6791378</v>
+        <v>6791433</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466756</v>
+        <v>124466718</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,47 +2690,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454999</v>
+        <v>455062</v>
       </c>
       <c r="R21" t="n">
-        <v>6791433</v>
+        <v>6791378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3836,10 +3836,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466751</v>
+        <v>124466728</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3848,47 +3848,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454956</v>
+        <v>454980</v>
       </c>
       <c r="R32" t="n">
-        <v>6791586</v>
+        <v>6791584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466728</v>
+        <v>124466751</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3959,38 +3950,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454980</v>
+        <v>454956</v>
       </c>
       <c r="R33" t="n">
-        <v>6791584</v>
+        <v>6791586</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466757</v>
+        <v>124466760</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454954</v>
+        <v>455024</v>
       </c>
       <c r="R6" t="n">
-        <v>6791589</v>
+        <v>6791525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466765</v>
+        <v>124466717</v>
       </c>
       <c r="B7" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455018</v>
+        <v>455070</v>
       </c>
       <c r="R7" t="n">
-        <v>6791399</v>
+        <v>6791371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466777</v>
+        <v>124466718</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454993</v>
+        <v>455062</v>
       </c>
       <c r="R8" t="n">
-        <v>6791588</v>
+        <v>6791378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466727</v>
+        <v>124466716</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,25 +1430,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454951</v>
+        <v>455041</v>
       </c>
       <c r="R9" t="n">
-        <v>6791583</v>
+        <v>6791358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466719</v>
+        <v>124466765</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455046</v>
+        <v>455018</v>
       </c>
       <c r="R10" t="n">
-        <v>6791403</v>
+        <v>6791399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466760</v>
+        <v>124466720</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,47 +1634,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455024</v>
+        <v>455013</v>
       </c>
       <c r="R11" t="n">
-        <v>6791525</v>
+        <v>6791456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466743</v>
+        <v>124466724</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,47 +1736,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454986</v>
+        <v>455029</v>
       </c>
       <c r="R12" t="n">
-        <v>6791588</v>
+        <v>6791510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466739</v>
+        <v>124466757</v>
       </c>
       <c r="B13" t="n">
-        <v>94959</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,38 +1838,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455032</v>
+        <v>454954</v>
       </c>
       <c r="R13" t="n">
-        <v>6791410</v>
+        <v>6791589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466758</v>
+        <v>124466777</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,47 +1949,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454965</v>
+        <v>454993</v>
       </c>
       <c r="R14" t="n">
-        <v>6791575</v>
+        <v>6791588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466713</v>
+        <v>124466741</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,38 +2051,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454998</v>
+        <v>454985</v>
       </c>
       <c r="R15" t="n">
-        <v>6791464</v>
+        <v>6791568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466763</v>
+        <v>124466723</v>
       </c>
       <c r="B16" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455022</v>
+        <v>455035</v>
       </c>
       <c r="R16" t="n">
-        <v>6791480</v>
+        <v>6791359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2252,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466723</v>
+        <v>124466727</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2301,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455035</v>
+        <v>454951</v>
       </c>
       <c r="R17" t="n">
-        <v>6791359</v>
+        <v>6791583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466724</v>
+        <v>124466751</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,38 +2366,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455029</v>
+        <v>454956</v>
       </c>
       <c r="R18" t="n">
-        <v>6791510</v>
+        <v>6791586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466725</v>
+        <v>124466763</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,21 +2481,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454951</v>
+        <v>455022</v>
       </c>
       <c r="R19" t="n">
-        <v>6791581</v>
+        <v>6791480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466756</v>
+        <v>124466776</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,47 +2579,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454999</v>
+        <v>454967</v>
       </c>
       <c r="R20" t="n">
-        <v>6791433</v>
+        <v>6791549</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466718</v>
+        <v>124466734</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,38 +2681,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455062</v>
+        <v>455027</v>
       </c>
       <c r="R21" t="n">
-        <v>6791378</v>
+        <v>6791520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466775</v>
+        <v>124466787</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,34 +2792,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454990</v>
+        <v>455074</v>
       </c>
       <c r="R22" t="n">
-        <v>6791542</v>
+        <v>6791202</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2857,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466716</v>
+        <v>124466745</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,38 +2900,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455041</v>
+        <v>454974</v>
       </c>
       <c r="R23" t="n">
-        <v>6791358</v>
+        <v>6791602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466745</v>
+        <v>124466746</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3033,10 +3048,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454974</v>
+        <v>454971</v>
       </c>
       <c r="R24" t="n">
-        <v>6791602</v>
+        <v>6791601</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,10 +3110,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466721</v>
+        <v>124466770</v>
       </c>
       <c r="B25" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3122,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3150,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454980</v>
+        <v>454999</v>
       </c>
       <c r="R25" t="n">
-        <v>6791584</v>
+        <v>6791433</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3212,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466753</v>
+        <v>124466738</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,47 +3224,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454960</v>
+        <v>454961</v>
       </c>
       <c r="R26" t="n">
-        <v>6791599</v>
+        <v>6791550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3314,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466740</v>
+        <v>124466754</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3343,7 +3349,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3357,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455036</v>
+        <v>454972</v>
       </c>
       <c r="R27" t="n">
-        <v>6791428</v>
+        <v>6791550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466746</v>
+        <v>124466740</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3454,7 +3460,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3468,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454971</v>
+        <v>455036</v>
       </c>
       <c r="R28" t="n">
-        <v>6791601</v>
+        <v>6791428</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466720</v>
+        <v>124466721</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3542,25 +3548,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3570,10 +3576,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455013</v>
+        <v>454980</v>
       </c>
       <c r="R29" t="n">
-        <v>6791456</v>
+        <v>6791584</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466770</v>
+        <v>124466739</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>94959</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,25 +3650,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454999</v>
+        <v>455032</v>
       </c>
       <c r="R30" t="n">
-        <v>6791433</v>
+        <v>6791410</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3734,7 +3740,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466776</v>
+        <v>124466771</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3774,10 +3780,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454967</v>
+        <v>455011</v>
       </c>
       <c r="R31" t="n">
-        <v>6791549</v>
+        <v>6791455</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3836,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466728</v>
+        <v>124466774</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3852,21 +3858,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3876,10 +3882,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454980</v>
+        <v>455009</v>
       </c>
       <c r="R32" t="n">
-        <v>6791584</v>
+        <v>6791499</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,7 +3944,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466751</v>
+        <v>124466761</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -3973,7 +3979,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3987,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454956</v>
+        <v>454973</v>
       </c>
       <c r="R33" t="n">
-        <v>6791586</v>
+        <v>6791596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466771</v>
+        <v>124466728</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,21 +4071,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455011</v>
+        <v>454980</v>
       </c>
       <c r="R34" t="n">
-        <v>6791455</v>
+        <v>6791584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,10 +4157,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466734</v>
+        <v>124466713</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>96354</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,39 +4173,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455027</v>
+        <v>454998</v>
       </c>
       <c r="R35" t="n">
-        <v>6791520</v>
+        <v>6791464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4258,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466754</v>
+        <v>124466725</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,47 +4271,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454972</v>
+        <v>454951</v>
       </c>
       <c r="R36" t="n">
-        <v>6791550</v>
+        <v>6791581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,10 +4361,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466761</v>
+        <v>124466785</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4381,35 +4373,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4418,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454973</v>
+        <v>455002</v>
       </c>
       <c r="R37" t="n">
-        <v>6791596</v>
+        <v>6791543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,10 +4468,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466717</v>
+        <v>124466758</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4492,38 +4480,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455070</v>
+        <v>454965</v>
       </c>
       <c r="R38" t="n">
-        <v>6791371</v>
+        <v>6791575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466785</v>
+        <v>124466753</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,31 +4591,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4627,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455002</v>
+        <v>454960</v>
       </c>
       <c r="R39" t="n">
-        <v>6791543</v>
+        <v>6791599</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466730</v>
+        <v>124466719</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4701,43 +4702,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455093</v>
+        <v>455046</v>
       </c>
       <c r="R40" t="n">
-        <v>6791177</v>
+        <v>6791403</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,11 +4766,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4801,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466738</v>
+        <v>124466775</v>
       </c>
       <c r="B41" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4813,25 +4804,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454961</v>
+        <v>454990</v>
       </c>
       <c r="R41" t="n">
-        <v>6791550</v>
+        <v>6791542</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,7 +4894,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466787</v>
+        <v>124466730</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4948,10 +4939,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455074</v>
+        <v>455093</v>
       </c>
       <c r="R42" t="n">
-        <v>6791202</v>
+        <v>6791177</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,7 +4979,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>tre bohål i granlåga</t>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,7 +5006,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466741</v>
+        <v>124466756</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5050,7 +5041,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5064,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454985</v>
+        <v>454999</v>
       </c>
       <c r="R43" t="n">
-        <v>6791568</v>
+        <v>6791433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466774</v>
+        <v>124466743</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,38 +5129,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455009</v>
+        <v>454986</v>
       </c>
       <c r="R44" t="n">
-        <v>6791499</v>
+        <v>6791588</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466760</v>
+        <v>124466757</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455024</v>
+        <v>454954</v>
       </c>
       <c r="R6" t="n">
-        <v>6791525</v>
+        <v>6791589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466717</v>
+        <v>124466724</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455070</v>
+        <v>455029</v>
       </c>
       <c r="R7" t="n">
-        <v>6791371</v>
+        <v>6791510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466718</v>
+        <v>124466777</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455062</v>
+        <v>454993</v>
       </c>
       <c r="R8" t="n">
-        <v>6791378</v>
+        <v>6791588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466716</v>
+        <v>124466723</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,25 +1430,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455041</v>
+        <v>455035</v>
       </c>
       <c r="R9" t="n">
-        <v>6791358</v>
+        <v>6791359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466765</v>
+        <v>124466774</v>
       </c>
       <c r="B10" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455018</v>
+        <v>455009</v>
       </c>
       <c r="R10" t="n">
-        <v>6791399</v>
+        <v>6791499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466720</v>
+        <v>124466727</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,25 +1634,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455013</v>
+        <v>454951</v>
       </c>
       <c r="R11" t="n">
-        <v>6791456</v>
+        <v>6791583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466724</v>
+        <v>124466761</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,38 +1736,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455029</v>
+        <v>454973</v>
       </c>
       <c r="R12" t="n">
-        <v>6791510</v>
+        <v>6791596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466757</v>
+        <v>124466716</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,47 +1847,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454954</v>
+        <v>455041</v>
       </c>
       <c r="R13" t="n">
-        <v>6791589</v>
+        <v>6791358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466777</v>
+        <v>124466728</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R14" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466741</v>
+        <v>124466738</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,47 +2051,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454985</v>
+        <v>454961</v>
       </c>
       <c r="R15" t="n">
-        <v>6791568</v>
+        <v>6791550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2141,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466723</v>
+        <v>124466743</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,38 +2153,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455035</v>
+        <v>454986</v>
       </c>
       <c r="R16" t="n">
-        <v>6791359</v>
+        <v>6791588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466727</v>
+        <v>124466713</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454951</v>
+        <v>454998</v>
       </c>
       <c r="R17" t="n">
-        <v>6791583</v>
+        <v>6791464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466751</v>
+        <v>124466771</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,47 +2366,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454956</v>
+        <v>455011</v>
       </c>
       <c r="R18" t="n">
-        <v>6791586</v>
+        <v>6791455</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466763</v>
+        <v>124466721</v>
       </c>
       <c r="B19" t="n">
-        <v>91026</v>
+        <v>91361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,25 +2468,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2505,10 +2496,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455022</v>
+        <v>454980</v>
       </c>
       <c r="R19" t="n">
-        <v>6791480</v>
+        <v>6791584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2567,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466776</v>
+        <v>124466717</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2570,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454967</v>
+        <v>455070</v>
       </c>
       <c r="R20" t="n">
-        <v>6791549</v>
+        <v>6791371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466734</v>
+        <v>124466725</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,39 +2676,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455027</v>
+        <v>454951</v>
       </c>
       <c r="R21" t="n">
-        <v>6791520</v>
+        <v>6791581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466787</v>
+        <v>124466741</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,31 +2774,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2821,10 +2811,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455074</v>
+        <v>454985</v>
       </c>
       <c r="R22" t="n">
-        <v>6791202</v>
+        <v>6791568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,11 +2847,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,7 +2873,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466745</v>
+        <v>124466753</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2923,7 +2908,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2937,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454974</v>
+        <v>454960</v>
       </c>
       <c r="R23" t="n">
-        <v>6791602</v>
+        <v>6791599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466746</v>
+        <v>124466763</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,47 +2996,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454971</v>
+        <v>455022</v>
       </c>
       <c r="R24" t="n">
-        <v>6791601</v>
+        <v>6791480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466770</v>
+        <v>124466765</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3126,21 +3102,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3150,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454999</v>
+        <v>455018</v>
       </c>
       <c r="R25" t="n">
-        <v>6791433</v>
+        <v>6791399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466738</v>
+        <v>124466718</v>
       </c>
       <c r="B26" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3228,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3252,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454961</v>
+        <v>455062</v>
       </c>
       <c r="R26" t="n">
-        <v>6791550</v>
+        <v>6791378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466754</v>
+        <v>124466756</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3349,7 +3325,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3363,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454972</v>
+        <v>454999</v>
       </c>
       <c r="R27" t="n">
-        <v>6791550</v>
+        <v>6791433</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3401,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466740</v>
+        <v>124466760</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3460,7 +3436,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3474,10 +3450,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455036</v>
+        <v>455024</v>
       </c>
       <c r="R28" t="n">
-        <v>6791428</v>
+        <v>6791525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466721</v>
+        <v>124466740</v>
       </c>
       <c r="B29" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,34 +3528,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454980</v>
+        <v>455036</v>
       </c>
       <c r="R29" t="n">
-        <v>6791584</v>
+        <v>6791428</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466771</v>
+        <v>124466719</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,25 +3737,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3780,10 +3765,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455011</v>
+        <v>455046</v>
       </c>
       <c r="R31" t="n">
-        <v>6791455</v>
+        <v>6791403</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3827,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466774</v>
+        <v>124466770</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3882,10 +3867,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455009</v>
+        <v>454999</v>
       </c>
       <c r="R32" t="n">
-        <v>6791499</v>
+        <v>6791433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466761</v>
+        <v>124466730</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,35 +3941,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3993,10 +3974,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454973</v>
+        <v>455093</v>
       </c>
       <c r="R33" t="n">
-        <v>6791596</v>
+        <v>6791177</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,6 +4010,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466728</v>
+        <v>124466734</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4071,34 +4057,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454980</v>
+        <v>455027</v>
       </c>
       <c r="R34" t="n">
-        <v>6791584</v>
+        <v>6791520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466713</v>
+        <v>124466720</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4169,25 +4160,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4197,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454998</v>
+        <v>455013</v>
       </c>
       <c r="R35" t="n">
-        <v>6791464</v>
+        <v>6791456</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4259,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466725</v>
+        <v>124466754</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4271,38 +4262,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454951</v>
+        <v>454972</v>
       </c>
       <c r="R36" t="n">
-        <v>6791581</v>
+        <v>6791550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466753</v>
+        <v>124466776</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4591,47 +4591,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454960</v>
+        <v>454967</v>
       </c>
       <c r="R39" t="n">
-        <v>6791599</v>
+        <v>6791549</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4690,10 +4681,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466719</v>
+        <v>124466751</v>
       </c>
       <c r="B40" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4702,38 +4693,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455046</v>
+        <v>454956</v>
       </c>
       <c r="R40" t="n">
-        <v>6791403</v>
+        <v>6791586</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466775</v>
+        <v>124466745</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4804,38 +4804,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454990</v>
+        <v>454974</v>
       </c>
       <c r="R41" t="n">
-        <v>6791542</v>
+        <v>6791602</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4894,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466730</v>
+        <v>124466775</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4910,39 +4919,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455093</v>
+        <v>454990</v>
       </c>
       <c r="R42" t="n">
-        <v>6791177</v>
+        <v>6791542</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4975,11 +4979,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5006,7 +5005,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466756</v>
+        <v>124466746</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5041,7 +5040,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5055,10 +5054,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454999</v>
+        <v>454971</v>
       </c>
       <c r="R43" t="n">
-        <v>6791433</v>
+        <v>6791601</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466743</v>
+        <v>124466787</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,35 +5128,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5166,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454986</v>
+        <v>455074</v>
       </c>
       <c r="R44" t="n">
-        <v>6791588</v>
+        <v>6791202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5202,6 +5197,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -3086,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466765</v>
+        <v>124466718</v>
       </c>
       <c r="B25" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455018</v>
+        <v>455062</v>
       </c>
       <c r="R25" t="n">
-        <v>6791399</v>
+        <v>6791378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466718</v>
+        <v>124466765</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455062</v>
+        <v>455018</v>
       </c>
       <c r="R26" t="n">
-        <v>6791378</v>
+        <v>6791399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466745</v>
+        <v>124466775</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4804,47 +4804,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454974</v>
+        <v>454990</v>
       </c>
       <c r="R41" t="n">
-        <v>6791602</v>
+        <v>6791542</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,10 +4894,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466775</v>
+        <v>124466745</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4915,38 +4906,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454990</v>
+        <v>454974</v>
       </c>
       <c r="R42" t="n">
-        <v>6791542</v>
+        <v>6791602</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466724</v>
+        <v>124466723</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455029</v>
+        <v>455035</v>
       </c>
       <c r="R7" t="n">
-        <v>6791510</v>
+        <v>6791359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466777</v>
+        <v>124466724</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454993</v>
+        <v>455029</v>
       </c>
       <c r="R8" t="n">
-        <v>6791588</v>
+        <v>6791510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466723</v>
+        <v>124466777</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455035</v>
+        <v>454993</v>
       </c>
       <c r="R9" t="n">
-        <v>6791359</v>
+        <v>6791588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466727</v>
+        <v>124466716</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,25 +1634,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454951</v>
+        <v>455041</v>
       </c>
       <c r="R11" t="n">
-        <v>6791583</v>
+        <v>6791358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466716</v>
+        <v>124466727</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,25 +1847,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455041</v>
+        <v>454951</v>
       </c>
       <c r="R13" t="n">
-        <v>6791358</v>
+        <v>6791583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466728</v>
+        <v>124466738</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,25 +1949,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454980</v>
+        <v>454961</v>
       </c>
       <c r="R14" t="n">
-        <v>6791584</v>
+        <v>6791550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466738</v>
+        <v>124466743</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,38 +2051,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454961</v>
+        <v>454986</v>
       </c>
       <c r="R15" t="n">
-        <v>6791550</v>
+        <v>6791588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466743</v>
+        <v>124466728</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,47 +2162,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454986</v>
+        <v>454980</v>
       </c>
       <c r="R16" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466718</v>
+        <v>124466765</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455062</v>
+        <v>455018</v>
       </c>
       <c r="R25" t="n">
-        <v>6791378</v>
+        <v>6791399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466765</v>
+        <v>124466718</v>
       </c>
       <c r="B26" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455018</v>
+        <v>455062</v>
       </c>
       <c r="R26" t="n">
-        <v>6791399</v>
+        <v>6791378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466720</v>
+        <v>124466785</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>5176</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,34 +4164,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455013</v>
+        <v>455002</v>
       </c>
       <c r="R35" t="n">
-        <v>6791456</v>
+        <v>6791543</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4361,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466785</v>
+        <v>124466720</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>90977</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4377,39 +4382,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455002</v>
+        <v>455013</v>
       </c>
       <c r="R37" t="n">
-        <v>6791543</v>
+        <v>6791456</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466757</v>
+        <v>124466754</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454954</v>
+        <v>454972</v>
       </c>
       <c r="R6" t="n">
-        <v>6791589</v>
+        <v>6791550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466723</v>
+        <v>124466740</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,38 +1226,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455035</v>
+        <v>455036</v>
       </c>
       <c r="R7" t="n">
-        <v>6791359</v>
+        <v>6791428</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466724</v>
+        <v>124466765</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455029</v>
+        <v>455018</v>
       </c>
       <c r="R8" t="n">
-        <v>6791510</v>
+        <v>6791399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466777</v>
+        <v>124466728</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R9" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466774</v>
+        <v>124466787</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,34 +1545,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455009</v>
+        <v>455074</v>
       </c>
       <c r="R10" t="n">
-        <v>6791499</v>
+        <v>6791202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,6 +1610,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466716</v>
+        <v>124466758</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,38 +1653,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455041</v>
+        <v>454965</v>
       </c>
       <c r="R11" t="n">
-        <v>6791358</v>
+        <v>6791575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466761</v>
+        <v>124466727</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,47 +1764,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454973</v>
+        <v>454951</v>
       </c>
       <c r="R12" t="n">
-        <v>6791596</v>
+        <v>6791583</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466727</v>
+        <v>124466777</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454951</v>
+        <v>454993</v>
       </c>
       <c r="R13" t="n">
-        <v>6791583</v>
+        <v>6791588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466738</v>
+        <v>124466771</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454961</v>
+        <v>455011</v>
       </c>
       <c r="R14" t="n">
-        <v>6791550</v>
+        <v>6791455</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466743</v>
+        <v>124466774</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,47 +2070,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454986</v>
+        <v>455009</v>
       </c>
       <c r="R15" t="n">
-        <v>6791588</v>
+        <v>6791499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466728</v>
+        <v>124466720</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454980</v>
+        <v>455013</v>
       </c>
       <c r="R16" t="n">
-        <v>6791584</v>
+        <v>6791456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466713</v>
+        <v>124466734</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,34 +2278,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454998</v>
+        <v>455027</v>
       </c>
       <c r="R17" t="n">
-        <v>6791464</v>
+        <v>6791520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466771</v>
+        <v>124466757</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,38 +2381,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455011</v>
+        <v>454954</v>
       </c>
       <c r="R18" t="n">
-        <v>6791455</v>
+        <v>6791589</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466721</v>
+        <v>124466723</v>
       </c>
       <c r="B19" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,25 +2492,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454980</v>
+        <v>455035</v>
       </c>
       <c r="R19" t="n">
-        <v>6791584</v>
+        <v>6791359</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466717</v>
+        <v>124466753</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,38 +2594,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455070</v>
+        <v>454960</v>
       </c>
       <c r="R20" t="n">
-        <v>6791371</v>
+        <v>6791599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466725</v>
+        <v>124466785</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2672,38 +2705,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454951</v>
+        <v>455002</v>
       </c>
       <c r="R21" t="n">
-        <v>6791581</v>
+        <v>6791543</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466741</v>
+        <v>124466713</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,47 +2812,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454985</v>
+        <v>454998</v>
       </c>
       <c r="R22" t="n">
-        <v>6791568</v>
+        <v>6791464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466753</v>
+        <v>124466725</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,47 +2914,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454960</v>
+        <v>454951</v>
       </c>
       <c r="R23" t="n">
-        <v>6791599</v>
+        <v>6791581</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466763</v>
+        <v>124466761</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,38 +3016,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455022</v>
+        <v>454973</v>
       </c>
       <c r="R24" t="n">
-        <v>6791480</v>
+        <v>6791596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,7 +3115,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466765</v>
+        <v>124466763</v>
       </c>
       <c r="B25" t="n">
         <v>91026</v>
@@ -3126,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455018</v>
+        <v>455022</v>
       </c>
       <c r="R25" t="n">
-        <v>6791399</v>
+        <v>6791480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466718</v>
+        <v>124466738</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3233,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455062</v>
+        <v>454961</v>
       </c>
       <c r="R26" t="n">
-        <v>6791378</v>
+        <v>6791550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,10 +3319,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466756</v>
+        <v>124466739</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3302,47 +3331,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454999</v>
+        <v>455032</v>
       </c>
       <c r="R27" t="n">
-        <v>6791433</v>
+        <v>6791410</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466760</v>
+        <v>124466717</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,47 +3433,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455024</v>
+        <v>455070</v>
       </c>
       <c r="R28" t="n">
-        <v>6791525</v>
+        <v>6791371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3523,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466740</v>
+        <v>124466756</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3547,7 +3558,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3561,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455036</v>
+        <v>454999</v>
       </c>
       <c r="R29" t="n">
-        <v>6791428</v>
+        <v>6791433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466739</v>
+        <v>124466775</v>
       </c>
       <c r="B30" t="n">
-        <v>94959</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3635,25 +3646,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455032</v>
+        <v>454990</v>
       </c>
       <c r="R30" t="n">
-        <v>6791410</v>
+        <v>6791542</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466719</v>
+        <v>124466776</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3737,25 +3748,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3765,10 +3776,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455046</v>
+        <v>454967</v>
       </c>
       <c r="R31" t="n">
-        <v>6791403</v>
+        <v>6791549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4041,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466734</v>
+        <v>124466724</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4057,39 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455027</v>
+        <v>455029</v>
       </c>
       <c r="R34" t="n">
-        <v>6791520</v>
+        <v>6791510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4148,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466785</v>
+        <v>124466721</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>91361</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,43 +4166,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455002</v>
+        <v>454980</v>
       </c>
       <c r="R35" t="n">
-        <v>6791543</v>
+        <v>6791584</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466754</v>
+        <v>124466716</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,47 +4268,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454972</v>
+        <v>455041</v>
       </c>
       <c r="R36" t="n">
-        <v>6791550</v>
+        <v>6791358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,7 +4358,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466720</v>
+        <v>124466718</v>
       </c>
       <c r="B37" t="n">
         <v>90977</v>
@@ -4406,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455013</v>
+        <v>455062</v>
       </c>
       <c r="R37" t="n">
-        <v>6791456</v>
+        <v>6791378</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4468,7 +4460,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466758</v>
+        <v>124466760</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4503,7 +4495,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4517,10 +4509,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454965</v>
+        <v>455024</v>
       </c>
       <c r="R38" t="n">
-        <v>6791575</v>
+        <v>6791525</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466776</v>
+        <v>124466751</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4591,38 +4583,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454967</v>
+        <v>454956</v>
       </c>
       <c r="R39" t="n">
-        <v>6791549</v>
+        <v>6791586</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4681,7 +4682,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466751</v>
+        <v>124466746</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4716,7 +4717,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4730,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454956</v>
+        <v>454971</v>
       </c>
       <c r="R40" t="n">
-        <v>6791586</v>
+        <v>6791601</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466775</v>
+        <v>124466719</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4804,25 +4805,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4832,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454990</v>
+        <v>455046</v>
       </c>
       <c r="R41" t="n">
-        <v>6791542</v>
+        <v>6791403</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5005,7 +5006,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466746</v>
+        <v>124466741</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5040,7 +5041,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5054,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454971</v>
+        <v>454985</v>
       </c>
       <c r="R43" t="n">
-        <v>6791601</v>
+        <v>6791568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5116,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466787</v>
+        <v>124466743</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5128,31 +5129,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5161,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455074</v>
+        <v>454986</v>
       </c>
       <c r="R44" t="n">
-        <v>6791202</v>
+        <v>6791588</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,11 +5202,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466754</v>
+        <v>124466719</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,47 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454972</v>
+        <v>455046</v>
       </c>
       <c r="R6" t="n">
-        <v>6791550</v>
+        <v>6791403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466740</v>
+        <v>124466725</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,47 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455036</v>
+        <v>454951</v>
       </c>
       <c r="R7" t="n">
-        <v>6791428</v>
+        <v>6791581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466765</v>
+        <v>124466775</v>
       </c>
       <c r="B8" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455018</v>
+        <v>454990</v>
       </c>
       <c r="R8" t="n">
-        <v>6791399</v>
+        <v>6791542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466728</v>
+        <v>124466743</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,38 +1421,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454980</v>
+        <v>454986</v>
       </c>
       <c r="R9" t="n">
-        <v>6791584</v>
+        <v>6791588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466787</v>
+        <v>124466770</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,39 +1536,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455074</v>
+        <v>454999</v>
       </c>
       <c r="R10" t="n">
-        <v>6791202</v>
+        <v>6791433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,11 +1596,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466758</v>
+        <v>124466746</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1676,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454965</v>
+        <v>454971</v>
       </c>
       <c r="R11" t="n">
-        <v>6791575</v>
+        <v>6791601</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466727</v>
+        <v>124466718</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,25 +1745,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454951</v>
+        <v>455062</v>
       </c>
       <c r="R12" t="n">
-        <v>6791583</v>
+        <v>6791378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466777</v>
+        <v>124466728</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,21 +1851,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R13" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466771</v>
+        <v>124466751</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,38 +1949,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455011</v>
+        <v>454956</v>
       </c>
       <c r="R14" t="n">
-        <v>6791455</v>
+        <v>6791586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466774</v>
+        <v>124466724</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455009</v>
+        <v>455029</v>
       </c>
       <c r="R15" t="n">
-        <v>6791499</v>
+        <v>6791510</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2150,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466720</v>
+        <v>124466716</v>
       </c>
       <c r="B16" t="n">
         <v>90977</v>
@@ -2200,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455013</v>
+        <v>455041</v>
       </c>
       <c r="R16" t="n">
-        <v>6791456</v>
+        <v>6791358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466734</v>
+        <v>124466720</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,43 +2264,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455027</v>
+        <v>455013</v>
       </c>
       <c r="R17" t="n">
-        <v>6791520</v>
+        <v>6791456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466757</v>
+        <v>124466785</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,35 +2366,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2418,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454954</v>
+        <v>455002</v>
       </c>
       <c r="R18" t="n">
-        <v>6791589</v>
+        <v>6791543</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466723</v>
+        <v>124466730</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,34 +2477,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455035</v>
+        <v>455093</v>
       </c>
       <c r="R19" t="n">
-        <v>6791359</v>
+        <v>6791177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,6 +2542,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,7 +2573,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466753</v>
+        <v>124466757</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2617,7 +2608,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2631,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454960</v>
+        <v>454954</v>
       </c>
       <c r="R20" t="n">
-        <v>6791599</v>
+        <v>6791589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466785</v>
+        <v>124466713</v>
       </c>
       <c r="B21" t="n">
-        <v>5176</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,43 +2696,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455002</v>
+        <v>454998</v>
       </c>
       <c r="R21" t="n">
-        <v>6791543</v>
+        <v>6791464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466713</v>
+        <v>124466758</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,38 +2798,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454998</v>
+        <v>454965</v>
       </c>
       <c r="R22" t="n">
-        <v>6791464</v>
+        <v>6791575</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466725</v>
+        <v>124466765</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454951</v>
+        <v>455018</v>
       </c>
       <c r="R23" t="n">
-        <v>6791581</v>
+        <v>6791399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466761</v>
+        <v>124466787</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3016,35 +3011,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3053,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454973</v>
+        <v>455074</v>
       </c>
       <c r="R24" t="n">
-        <v>6791596</v>
+        <v>6791202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,6 +3080,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3115,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466763</v>
+        <v>124466717</v>
       </c>
       <c r="B25" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,25 +3123,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455022</v>
+        <v>455070</v>
       </c>
       <c r="R25" t="n">
-        <v>6791480</v>
+        <v>6791371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466738</v>
+        <v>124466745</v>
       </c>
       <c r="B26" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,38 +3225,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454961</v>
+        <v>454974</v>
       </c>
       <c r="R26" t="n">
-        <v>6791550</v>
+        <v>6791602</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466739</v>
+        <v>124466754</v>
       </c>
       <c r="B27" t="n">
-        <v>94959</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,38 +3336,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455032</v>
+        <v>454972</v>
       </c>
       <c r="R27" t="n">
-        <v>6791410</v>
+        <v>6791550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466717</v>
+        <v>124466721</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,25 +3447,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3461,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455070</v>
+        <v>454980</v>
       </c>
       <c r="R28" t="n">
-        <v>6791371</v>
+        <v>6791584</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466756</v>
+        <v>124466777</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,47 +3549,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454999</v>
+        <v>454993</v>
       </c>
       <c r="R29" t="n">
-        <v>6791433</v>
+        <v>6791588</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466775</v>
+        <v>124466738</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454990</v>
+        <v>454961</v>
       </c>
       <c r="R30" t="n">
-        <v>6791542</v>
+        <v>6791550</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466776</v>
+        <v>124466753</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,38 +3753,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454967</v>
+        <v>454960</v>
       </c>
       <c r="R31" t="n">
-        <v>6791549</v>
+        <v>6791599</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3852,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466770</v>
+        <v>124466774</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3878,10 +3892,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454999</v>
+        <v>455009</v>
       </c>
       <c r="R32" t="n">
-        <v>6791433</v>
+        <v>6791499</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466730</v>
+        <v>124466723</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,39 +3970,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455093</v>
+        <v>455035</v>
       </c>
       <c r="R33" t="n">
-        <v>6791177</v>
+        <v>6791359</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4021,11 +4030,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,10 +4056,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466724</v>
+        <v>124466756</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,38 +4068,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455029</v>
+        <v>454999</v>
       </c>
       <c r="R34" t="n">
-        <v>6791510</v>
+        <v>6791433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466721</v>
+        <v>124466776</v>
       </c>
       <c r="B35" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,25 +4179,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454980</v>
+        <v>454967</v>
       </c>
       <c r="R35" t="n">
-        <v>6791584</v>
+        <v>6791549</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466716</v>
+        <v>124466740</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4268,38 +4281,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455041</v>
+        <v>455036</v>
       </c>
       <c r="R36" t="n">
-        <v>6791358</v>
+        <v>6791428</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466718</v>
+        <v>124466771</v>
       </c>
       <c r="B37" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4370,25 +4392,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455062</v>
+        <v>455011</v>
       </c>
       <c r="R37" t="n">
-        <v>6791378</v>
+        <v>6791455</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466760</v>
+        <v>124466734</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,35 +4494,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4509,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455024</v>
+        <v>455027</v>
       </c>
       <c r="R38" t="n">
-        <v>6791525</v>
+        <v>6791520</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,7 +4589,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466751</v>
+        <v>124466761</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4606,7 +4624,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4620,10 +4638,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454956</v>
+        <v>454973</v>
       </c>
       <c r="R39" t="n">
-        <v>6791586</v>
+        <v>6791596</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4682,7 +4700,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466746</v>
+        <v>124466741</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4717,7 +4735,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4731,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454971</v>
+        <v>454985</v>
       </c>
       <c r="R40" t="n">
-        <v>6791601</v>
+        <v>6791568</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4793,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466719</v>
+        <v>124466727</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4805,25 +4823,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455046</v>
+        <v>454951</v>
       </c>
       <c r="R41" t="n">
-        <v>6791403</v>
+        <v>6791583</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466745</v>
+        <v>124466760</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4930,7 +4948,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4944,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454974</v>
+        <v>455024</v>
       </c>
       <c r="R42" t="n">
-        <v>6791602</v>
+        <v>6791525</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,10 +5024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466741</v>
+        <v>124466763</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,47 +5036,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454985</v>
+        <v>455022</v>
       </c>
       <c r="R43" t="n">
-        <v>6791568</v>
+        <v>6791480</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,10 +5126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466743</v>
+        <v>124466739</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>94959</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,47 +5138,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454986</v>
+        <v>455032</v>
       </c>
       <c r="R44" t="n">
-        <v>6791588</v>
+        <v>6791410</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466719</v>
+        <v>124466776</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455046</v>
+        <v>454967</v>
       </c>
       <c r="R6" t="n">
-        <v>6791403</v>
+        <v>6791549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466725</v>
+        <v>124466724</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454951</v>
+        <v>455029</v>
       </c>
       <c r="R7" t="n">
-        <v>6791581</v>
+        <v>6791510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466775</v>
+        <v>124466745</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,38 +1319,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454990</v>
+        <v>454974</v>
       </c>
       <c r="R8" t="n">
-        <v>6791542</v>
+        <v>6791602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466743</v>
+        <v>124466787</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,35 +1430,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454986</v>
+        <v>455074</v>
       </c>
       <c r="R9" t="n">
-        <v>6791588</v>
+        <v>6791202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1499,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,7 +1530,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466770</v>
+        <v>124466775</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1560,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454999</v>
+        <v>454990</v>
       </c>
       <c r="R10" t="n">
-        <v>6791433</v>
+        <v>6791542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466746</v>
+        <v>124466728</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,47 +1644,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454971</v>
+        <v>454980</v>
       </c>
       <c r="R11" t="n">
-        <v>6791601</v>
+        <v>6791584</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466718</v>
+        <v>124466785</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,34 +1750,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455062</v>
+        <v>455002</v>
       </c>
       <c r="R12" t="n">
-        <v>6791378</v>
+        <v>6791543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466728</v>
+        <v>124466741</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,38 +1853,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454980</v>
+        <v>454985</v>
       </c>
       <c r="R13" t="n">
-        <v>6791584</v>
+        <v>6791568</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466751</v>
+        <v>124466771</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,47 +1964,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454956</v>
+        <v>455011</v>
       </c>
       <c r="R14" t="n">
-        <v>6791586</v>
+        <v>6791455</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466724</v>
+        <v>124466734</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,34 +2070,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455029</v>
+        <v>455027</v>
       </c>
       <c r="R15" t="n">
-        <v>6791510</v>
+        <v>6791520</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466716</v>
+        <v>124466738</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455041</v>
+        <v>454961</v>
       </c>
       <c r="R16" t="n">
-        <v>6791358</v>
+        <v>6791550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466720</v>
+        <v>124466761</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,38 +2275,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455013</v>
+        <v>454973</v>
       </c>
       <c r="R17" t="n">
-        <v>6791456</v>
+        <v>6791596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2374,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466785</v>
+        <v>124466717</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,39 +2390,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455002</v>
+        <v>455070</v>
       </c>
       <c r="R18" t="n">
-        <v>6791543</v>
+        <v>6791371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466730</v>
+        <v>124466723</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,39 +2492,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455093</v>
+        <v>455035</v>
       </c>
       <c r="R19" t="n">
-        <v>6791177</v>
+        <v>6791359</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,11 +2552,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,7 +2578,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466757</v>
+        <v>124466746</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2608,7 +2613,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2622,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454954</v>
+        <v>454971</v>
       </c>
       <c r="R20" t="n">
-        <v>6791589</v>
+        <v>6791601</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466713</v>
+        <v>124466758</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,38 +2701,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454998</v>
+        <v>454965</v>
       </c>
       <c r="R21" t="n">
-        <v>6791464</v>
+        <v>6791575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466758</v>
+        <v>124466716</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2798,47 +2812,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454965</v>
+        <v>455041</v>
       </c>
       <c r="R22" t="n">
-        <v>6791575</v>
+        <v>6791358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466765</v>
+        <v>124466718</v>
       </c>
       <c r="B23" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2909,25 +2914,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455018</v>
+        <v>455062</v>
       </c>
       <c r="R23" t="n">
-        <v>6791399</v>
+        <v>6791378</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466787</v>
+        <v>124466719</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,43 +3016,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455074</v>
+        <v>455046</v>
       </c>
       <c r="R24" t="n">
-        <v>6791202</v>
+        <v>6791403</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3080,11 +3080,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466717</v>
+        <v>124466730</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,38 +3118,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455070</v>
+        <v>455093</v>
       </c>
       <c r="R25" t="n">
-        <v>6791371</v>
+        <v>6791177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466745</v>
+        <v>124466751</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454974</v>
+        <v>454956</v>
       </c>
       <c r="R26" t="n">
-        <v>6791602</v>
+        <v>6791586</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,10 +3329,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466754</v>
+        <v>124466713</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,47 +3341,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454972</v>
+        <v>454998</v>
       </c>
       <c r="R27" t="n">
-        <v>6791550</v>
+        <v>6791464</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466721</v>
+        <v>124466765</v>
       </c>
       <c r="B28" t="n">
-        <v>91361</v>
+        <v>91026</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454980</v>
+        <v>455018</v>
       </c>
       <c r="R28" t="n">
-        <v>6791584</v>
+        <v>6791399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3533,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466777</v>
+        <v>124466727</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454993</v>
+        <v>454951</v>
       </c>
       <c r="R29" t="n">
-        <v>6791588</v>
+        <v>6791583</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466738</v>
+        <v>124466777</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3647,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454961</v>
+        <v>454993</v>
       </c>
       <c r="R30" t="n">
-        <v>6791550</v>
+        <v>6791588</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3737,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466753</v>
+        <v>124466760</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3776,7 +3772,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3790,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454960</v>
+        <v>455024</v>
       </c>
       <c r="R31" t="n">
-        <v>6791599</v>
+        <v>6791525</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466774</v>
+        <v>124466743</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,38 +3860,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455009</v>
+        <v>454986</v>
       </c>
       <c r="R32" t="n">
-        <v>6791499</v>
+        <v>6791588</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466723</v>
+        <v>124466739</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>94959</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,25 +3971,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455035</v>
+        <v>455032</v>
       </c>
       <c r="R33" t="n">
-        <v>6791359</v>
+        <v>6791410</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4056,7 +4061,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466756</v>
+        <v>124466753</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4091,7 +4096,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454999</v>
+        <v>454960</v>
       </c>
       <c r="R34" t="n">
-        <v>6791433</v>
+        <v>6791599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466776</v>
+        <v>124466740</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,38 +4184,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454967</v>
+        <v>455036</v>
       </c>
       <c r="R35" t="n">
-        <v>6791549</v>
+        <v>6791428</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466740</v>
+        <v>124466774</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,47 +4295,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455036</v>
+        <v>455009</v>
       </c>
       <c r="R36" t="n">
-        <v>6791428</v>
+        <v>6791499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466771</v>
+        <v>124466754</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4392,38 +4397,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455011</v>
+        <v>454972</v>
       </c>
       <c r="R37" t="n">
-        <v>6791455</v>
+        <v>6791550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,10 +4496,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466734</v>
+        <v>124466757</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4494,31 +4508,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4527,10 +4545,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455027</v>
+        <v>454954</v>
       </c>
       <c r="R38" t="n">
-        <v>6791520</v>
+        <v>6791589</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466761</v>
+        <v>124466720</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,47 +4619,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454973</v>
+        <v>455013</v>
       </c>
       <c r="R39" t="n">
-        <v>6791596</v>
+        <v>6791456</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466741</v>
+        <v>124466725</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,47 +4721,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454985</v>
+        <v>454951</v>
       </c>
       <c r="R40" t="n">
-        <v>6791568</v>
+        <v>6791581</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466727</v>
+        <v>124466763</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454951</v>
+        <v>455022</v>
       </c>
       <c r="R41" t="n">
-        <v>6791583</v>
+        <v>6791480</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466760</v>
+        <v>124466721</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,43 +4929,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455024</v>
+        <v>454980</v>
       </c>
       <c r="R42" t="n">
-        <v>6791525</v>
+        <v>6791584</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5024,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466763</v>
+        <v>124466770</v>
       </c>
       <c r="B43" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5040,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455022</v>
+        <v>454999</v>
       </c>
       <c r="R43" t="n">
-        <v>6791480</v>
+        <v>6791433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466739</v>
+        <v>124466756</v>
       </c>
       <c r="B44" t="n">
-        <v>94959</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,38 +5129,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455032</v>
+        <v>454999</v>
       </c>
       <c r="R44" t="n">
-        <v>6791410</v>
+        <v>6791433</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466724</v>
+        <v>124466746</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455029</v>
+        <v>454971</v>
       </c>
       <c r="R7" t="n">
-        <v>6791510</v>
+        <v>6791601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466745</v>
+        <v>124466758</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1342,7 +1351,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1356,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454974</v>
+        <v>454965</v>
       </c>
       <c r="R8" t="n">
-        <v>6791602</v>
+        <v>6791575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466787</v>
+        <v>124466740</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,31 +1439,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455074</v>
+        <v>455036</v>
       </c>
       <c r="R9" t="n">
-        <v>6791202</v>
+        <v>6791428</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,11 +1512,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466775</v>
+        <v>124466713</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454990</v>
+        <v>454998</v>
       </c>
       <c r="R10" t="n">
-        <v>6791542</v>
+        <v>6791464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466728</v>
+        <v>124466738</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,25 +1652,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454980</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6791584</v>
+        <v>6791550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466785</v>
+        <v>124466719</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,39 +1758,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455002</v>
+        <v>455046</v>
       </c>
       <c r="R12" t="n">
-        <v>6791543</v>
+        <v>6791403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466741</v>
+        <v>124466721</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,43 +1860,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454985</v>
+        <v>454980</v>
       </c>
       <c r="R13" t="n">
-        <v>6791568</v>
+        <v>6791584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466734</v>
+        <v>124466774</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,39 +2064,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455027</v>
+        <v>455009</v>
       </c>
       <c r="R15" t="n">
-        <v>6791520</v>
+        <v>6791499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466738</v>
+        <v>124466734</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,38 +2162,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454961</v>
+        <v>455027</v>
       </c>
       <c r="R16" t="n">
-        <v>6791550</v>
+        <v>6791520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2257,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466761</v>
+        <v>124466754</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2298,7 +2292,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2312,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454973</v>
+        <v>454972</v>
       </c>
       <c r="R17" t="n">
-        <v>6791596</v>
+        <v>6791550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466717</v>
+        <v>124466743</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2386,38 +2380,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455070</v>
+        <v>454986</v>
       </c>
       <c r="R18" t="n">
-        <v>6791371</v>
+        <v>6791588</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466723</v>
+        <v>124466761</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2488,38 +2491,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455035</v>
+        <v>454973</v>
       </c>
       <c r="R19" t="n">
-        <v>6791359</v>
+        <v>6791596</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466746</v>
+        <v>124466775</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,47 +2602,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454971</v>
+        <v>454990</v>
       </c>
       <c r="R20" t="n">
-        <v>6791601</v>
+        <v>6791542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466758</v>
+        <v>124466770</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,47 +2704,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454965</v>
+        <v>454999</v>
       </c>
       <c r="R21" t="n">
-        <v>6791575</v>
+        <v>6791433</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2794,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466716</v>
+        <v>124466753</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,38 +2806,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455041</v>
+        <v>454960</v>
       </c>
       <c r="R22" t="n">
-        <v>6791358</v>
+        <v>6791599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466718</v>
+        <v>124466777</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2914,25 +2917,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455062</v>
+        <v>454993</v>
       </c>
       <c r="R23" t="n">
-        <v>6791378</v>
+        <v>6791588</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466719</v>
+        <v>124466763</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3016,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455046</v>
+        <v>455022</v>
       </c>
       <c r="R24" t="n">
-        <v>6791403</v>
+        <v>6791480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466730</v>
+        <v>124466785</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,31 +3121,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3151,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455093</v>
+        <v>455002</v>
       </c>
       <c r="R25" t="n">
-        <v>6791177</v>
+        <v>6791543</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3190,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124466751</v>
+        <v>124466723</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3230,47 +3228,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454956</v>
+        <v>455035</v>
       </c>
       <c r="R26" t="n">
-        <v>6791586</v>
+        <v>6791359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3329,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466713</v>
+        <v>124466760</v>
       </c>
       <c r="B27" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,38 +3330,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454998</v>
+        <v>455024</v>
       </c>
       <c r="R27" t="n">
-        <v>6791464</v>
+        <v>6791525</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466765</v>
+        <v>124466717</v>
       </c>
       <c r="B28" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3441,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455018</v>
+        <v>455070</v>
       </c>
       <c r="R28" t="n">
-        <v>6791399</v>
+        <v>6791371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124466727</v>
+        <v>124466741</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3545,38 +3543,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454951</v>
+        <v>454985</v>
       </c>
       <c r="R29" t="n">
-        <v>6791583</v>
+        <v>6791568</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466777</v>
+        <v>124466728</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,21 +3658,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3675,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454993</v>
+        <v>454980</v>
       </c>
       <c r="R30" t="n">
-        <v>6791588</v>
+        <v>6791584</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466760</v>
+        <v>124466787</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,35 +3756,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3786,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455024</v>
+        <v>455074</v>
       </c>
       <c r="R31" t="n">
-        <v>6791525</v>
+        <v>6791202</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3825,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466743</v>
+        <v>124466724</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,47 +3868,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454986</v>
+        <v>455029</v>
       </c>
       <c r="R32" t="n">
-        <v>6791588</v>
+        <v>6791510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4061,10 +4060,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466753</v>
+        <v>124466765</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,47 +4072,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454960</v>
+        <v>455018</v>
       </c>
       <c r="R34" t="n">
-        <v>6791599</v>
+        <v>6791399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4172,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466740</v>
+        <v>124466727</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,47 +4174,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455036</v>
+        <v>454951</v>
       </c>
       <c r="R35" t="n">
-        <v>6791428</v>
+        <v>6791583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4264,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466774</v>
+        <v>124466718</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4295,25 +4276,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455009</v>
+        <v>455062</v>
       </c>
       <c r="R36" t="n">
-        <v>6791499</v>
+        <v>6791378</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4366,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466754</v>
+        <v>124466756</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4420,7 +4401,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4434,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454972</v>
+        <v>454999</v>
       </c>
       <c r="R37" t="n">
-        <v>6791550</v>
+        <v>6791433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,10 +4477,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466757</v>
+        <v>124466725</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,47 +4489,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454954</v>
+        <v>454951</v>
       </c>
       <c r="R38" t="n">
-        <v>6791589</v>
+        <v>6791581</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466720</v>
+        <v>124466751</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4619,38 +4591,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455013</v>
+        <v>454956</v>
       </c>
       <c r="R39" t="n">
-        <v>6791456</v>
+        <v>6791586</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466725</v>
+        <v>124466730</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,34 +4706,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454951</v>
+        <v>455093</v>
       </c>
       <c r="R40" t="n">
-        <v>6791581</v>
+        <v>6791177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,6 +4771,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,10 +4802,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466763</v>
+        <v>124466716</v>
       </c>
       <c r="B41" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,25 +4814,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455022</v>
+        <v>455041</v>
       </c>
       <c r="R41" t="n">
-        <v>6791480</v>
+        <v>6791358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466721</v>
+        <v>124466720</v>
       </c>
       <c r="B42" t="n">
-        <v>91361</v>
+        <v>90977</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4925,25 +4916,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4953,10 +4944,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454980</v>
+        <v>455013</v>
       </c>
       <c r="R42" t="n">
-        <v>6791584</v>
+        <v>6791456</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466770</v>
+        <v>124466745</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,38 +5018,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454999</v>
+        <v>454974</v>
       </c>
       <c r="R43" t="n">
-        <v>6791433</v>
+        <v>6791602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466756</v>
+        <v>124466757</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454999</v>
+        <v>454954</v>
       </c>
       <c r="R44" t="n">
-        <v>6791433</v>
+        <v>6791589</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 5813-2025 artfynd.xlsx
+++ b/artfynd/A 5813-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466776</v>
+        <v>124466763</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454967</v>
+        <v>455022</v>
       </c>
       <c r="R6" t="n">
-        <v>6791549</v>
+        <v>6791480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466746</v>
+        <v>124466785</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,35 +1217,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1254,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454971</v>
+        <v>455002</v>
       </c>
       <c r="R7" t="n">
-        <v>6791601</v>
+        <v>6791543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466758</v>
+        <v>124466751</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1351,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1365,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454965</v>
+        <v>454956</v>
       </c>
       <c r="R8" t="n">
-        <v>6791575</v>
+        <v>6791586</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466740</v>
+        <v>124466754</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1462,7 +1458,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455036</v>
+        <v>454972</v>
       </c>
       <c r="R9" t="n">
-        <v>6791428</v>
+        <v>6791550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466713</v>
+        <v>124466730</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,34 +1550,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454998</v>
+        <v>455093</v>
       </c>
       <c r="R10" t="n">
-        <v>6791464</v>
+        <v>6791177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1615,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466738</v>
+        <v>124466740</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,38 +1658,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>455036</v>
       </c>
       <c r="R11" t="n">
-        <v>6791550</v>
+        <v>6791428</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466719</v>
+        <v>124466721</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1769,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455046</v>
+        <v>454980</v>
       </c>
       <c r="R12" t="n">
-        <v>6791403</v>
+        <v>6791584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466721</v>
+        <v>124466739</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>94959</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,25 +1871,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>2387</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454980</v>
+        <v>455032</v>
       </c>
       <c r="R13" t="n">
-        <v>6791584</v>
+        <v>6791410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466771</v>
+        <v>124466758</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,38 +1973,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455011</v>
+        <v>454965</v>
       </c>
       <c r="R14" t="n">
-        <v>6791455</v>
+        <v>6791575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466774</v>
+        <v>124466719</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,25 +2084,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455009</v>
+        <v>455046</v>
       </c>
       <c r="R15" t="n">
-        <v>6791499</v>
+        <v>6791403</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466734</v>
+        <v>124466771</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,39 +2190,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455027</v>
+        <v>455011</v>
       </c>
       <c r="R16" t="n">
-        <v>6791520</v>
+        <v>6791455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,7 +2276,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466754</v>
+        <v>124466760</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2292,7 +2311,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2306,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454972</v>
+        <v>455024</v>
       </c>
       <c r="R17" t="n">
-        <v>6791550</v>
+        <v>6791525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466743</v>
+        <v>124466745</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2403,7 +2422,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2417,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454986</v>
+        <v>454974</v>
       </c>
       <c r="R18" t="n">
-        <v>6791588</v>
+        <v>6791602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2498,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466761</v>
+        <v>124466757</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2514,7 +2533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2528,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454973</v>
+        <v>454954</v>
       </c>
       <c r="R19" t="n">
-        <v>6791596</v>
+        <v>6791589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,7 +2609,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124466775</v>
+        <v>124466770</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2630,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454990</v>
+        <v>454999</v>
       </c>
       <c r="R20" t="n">
-        <v>6791542</v>
+        <v>6791433</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124466770</v>
+        <v>124466777</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2732,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454999</v>
+        <v>454993</v>
       </c>
       <c r="R21" t="n">
-        <v>6791433</v>
+        <v>6791588</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124466753</v>
+        <v>124466724</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,47 +2825,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454960</v>
+        <v>455029</v>
       </c>
       <c r="R22" t="n">
-        <v>6791599</v>
+        <v>6791510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466777</v>
+        <v>124466743</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,35 +2927,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454993</v>
+        <v>454986</v>
       </c>
       <c r="R23" t="n">
         <v>6791588</v>
@@ -3007,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124466763</v>
+        <v>124466753</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,38 +3038,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455022</v>
+        <v>454960</v>
       </c>
       <c r="R24" t="n">
-        <v>6791480</v>
+        <v>6791599</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,10 +3137,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124466785</v>
+        <v>124466761</v>
       </c>
       <c r="B25" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3121,31 +3149,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3154,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455002</v>
+        <v>454973</v>
       </c>
       <c r="R25" t="n">
-        <v>6791543</v>
+        <v>6791596</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124466760</v>
+        <v>124466774</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,47 +3362,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455024</v>
+        <v>455009</v>
       </c>
       <c r="R27" t="n">
-        <v>6791525</v>
+        <v>6791499</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124466717</v>
+        <v>124466718</v>
       </c>
       <c r="B28" t="n">
         <v>90977</v>
@@ -3469,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455070</v>
+        <v>455062</v>
       </c>
       <c r="R28" t="n">
-        <v>6791371</v>
+        <v>6791378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124466728</v>
+        <v>124466716</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,25 +3677,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454980</v>
+        <v>455041</v>
       </c>
       <c r="R30" t="n">
-        <v>6791584</v>
+        <v>6791358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3744,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124466787</v>
+        <v>124466734</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3760,16 +3783,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3780,7 +3803,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3789,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455074</v>
+        <v>455027</v>
       </c>
       <c r="R31" t="n">
-        <v>6791202</v>
+        <v>6791520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,11 +3848,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124466724</v>
+        <v>124466738</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3868,25 +3886,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3896,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455029</v>
+        <v>454961</v>
       </c>
       <c r="R32" t="n">
-        <v>6791510</v>
+        <v>6791550</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3958,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124466739</v>
+        <v>124466776</v>
       </c>
       <c r="B33" t="n">
-        <v>94959</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,25 +3988,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3998,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455032</v>
+        <v>454967</v>
       </c>
       <c r="R33" t="n">
-        <v>6791410</v>
+        <v>6791549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124466765</v>
+        <v>124466713</v>
       </c>
       <c r="B34" t="n">
-        <v>91026</v>
+        <v>96354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4076,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4100,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455018</v>
+        <v>454998</v>
       </c>
       <c r="R34" t="n">
-        <v>6791399</v>
+        <v>6791464</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4162,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124466727</v>
+        <v>124466787</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4178,34 +4196,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454951</v>
+        <v>455074</v>
       </c>
       <c r="R35" t="n">
-        <v>6791583</v>
+        <v>6791202</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,6 +4261,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>tre bohål i granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4264,7 +4292,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124466718</v>
+        <v>124466717</v>
       </c>
       <c r="B36" t="n">
         <v>90977</v>
@@ -4304,10 +4332,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455062</v>
+        <v>455070</v>
       </c>
       <c r="R36" t="n">
-        <v>6791378</v>
+        <v>6791371</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,10 +4394,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124466756</v>
+        <v>124466775</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4378,47 +4406,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454999</v>
+        <v>454990</v>
       </c>
       <c r="R37" t="n">
-        <v>6791433</v>
+        <v>6791542</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,7 +4496,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124466725</v>
+        <v>124466727</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4520,7 +4539,7 @@
         <v>454951</v>
       </c>
       <c r="R38" t="n">
-        <v>6791581</v>
+        <v>6791583</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124466751</v>
+        <v>124466725</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4591,47 +4610,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454956</v>
+        <v>454951</v>
       </c>
       <c r="R39" t="n">
-        <v>6791586</v>
+        <v>6791581</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4690,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124466730</v>
+        <v>124466756</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4702,31 +4712,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4735,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455093</v>
+        <v>454999</v>
       </c>
       <c r="R40" t="n">
-        <v>6791177</v>
+        <v>6791433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4771,11 +4785,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>låga med bohål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4802,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124466716</v>
+        <v>124466746</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,38 +4823,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455041</v>
+        <v>454971</v>
       </c>
       <c r="R41" t="n">
-        <v>6791358</v>
+        <v>6791601</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4922,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124466720</v>
+        <v>124466765</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>91026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,25 +4934,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4944,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455013</v>
+        <v>455018</v>
       </c>
       <c r="R42" t="n">
-        <v>6791456</v>
+        <v>6791399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,10 +5024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124466745</v>
+        <v>124466728</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,47 +5036,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454974</v>
+        <v>454980</v>
       </c>
       <c r="R43" t="n">
-        <v>6791602</v>
+        <v>6791584</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,10 +5126,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124466757</v>
+        <v>124466720</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,47 +5138,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454954</v>
+        <v>455013</v>
       </c>
       <c r="R44" t="n">
-        <v>6791589</v>
+        <v>6791456</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
